--- a/plan_adressage.xlsx
+++ b/plan_adressage.xlsx
@@ -4649,7 +4649,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>CORE-1 Gi0/4</t>
+          <t>CORE-1 Gi1/0</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>CORE-1 Gi0/5</t>
+          <t>CORE-1 Gi1/1</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -4713,7 +4713,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>CORE-1 Gi0/6</t>
+          <t>CORE-1 Gi1/2</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -4745,7 +4745,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>CORE-1 Gi0/7</t>
+          <t>CORE-1 Gi1/3</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>CORE-2 Gi0/4</t>
+          <t>CORE-2 Gi1/0</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -4809,7 +4809,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>CORE-2 Gi0/5</t>
+          <t>CORE-2 Gi1/1</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -4841,7 +4841,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>CORE-2 Gi0/6</t>
+          <t>CORE-2 Gi1/2</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -4873,7 +4873,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>CORE-2 Gi0/7</t>
+          <t>CORE-2 Gi1/3</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">

--- a/plan_adressage.xlsx
+++ b/plan_adressage.xlsx
@@ -15,11 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-PROD" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-DMZ" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-ADMIN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MGMT" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VRF" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routage" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalabilité" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-SOC" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MGMT" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VRF" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routage" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalabilité" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -689,7 +690,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -937,113 +937,158 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Outillage admin : CICD, monitoring, SOC, AAA, vault</t>
+          <t>Outillage admin : CICD, observabilité, AAA, Vault, automation</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Inclut VLAN SOC isolé</t>
+          <t>SOC promu en VRF-SOC dédiée (voir bloc DC — VRF-SOC)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>DC — VRF-SOC</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>10.5.0.0/16</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>10.5.0.0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>10.5.255.255</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>65 536 IPs</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Cellule SOC (SIEM, NSM, TI, SIRP, SOAR) — VRF dédiée</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Promu depuis ADMIN : sensibilité maximale, polarité 'tout le SI → SOC'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Management</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>10.254.0.0/16</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>10.254.0.0</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>10.254.255.255</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>65 536 IPs</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>VRF-MGMT in-band équipements (switches, FW, HV)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Un seul /24 suffit, beaucoup de marge</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>WAN + bloc public simulé</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>192.168.122.0/24</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>192.168.122.0</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>192.168.122.255</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>256 IPs</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Subnet libvirt fusionnant peering PE↔FW et bloc public (VIP CARP de services)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>1 (imposé)</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Simplification lab : en prod, 2 plages distinctes (peering /30 + public /28)</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
@@ -1211,7 +1256,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>50000 + offset VRF (50001 PROD, 50002 DMZ, 50003 ADMIN, 50004 MGMT)</t>
+          <t>50000 + offset VRF (50001 PROD, 50002 DMZ, 50003 ADMIN, 50004 MGMT, 50005 SOC)</t>
         </is>
       </c>
       <c r="C23" s="17" t="n"/>
@@ -1241,6 +1286,7 @@
       <c r="H24" s="17" t="n"/>
       <c r="I24" s="18" t="n"/>
     </row>
+    <row r="25"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="B18:I18"/>
@@ -1264,6 +1310,654 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VRF-MGMT — management in-band des équipements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>VLAN 999 étendu dans la fabric via VXLAN. Contient uniquement les interfaces d'administration des équipements réseau et des hyperviseurs. Aucune VM applicative ici. Accès strictement filtré depuis la VRF-ADMIN via bastion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Plage réservée</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Préfixe</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>10.254.0.0/24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>IP début</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>10.254.0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>IP fin</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>10.254.0.255</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>VLAN</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>VNI L2</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>10999</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Plan IP management</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Équipement</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>SPINE-1</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Management1 (VRF MGMT)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.1/24</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Arista</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>SPINE-2</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Management1</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.2/24</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Arista</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Management1</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.11/24</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Arista</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Management1</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.12/24</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Arista</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-3</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Management1</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.13/24</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Arista</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>CORE-1</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.21/24</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>CORE-2</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.22/24</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>DIST-1</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.31/24</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>DIST-2</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.32/24</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>DIST-3</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.33/24</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>DIST-4</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.34/24</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>ACC-1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.41/24</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>ACC-2</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.42/24</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>ACC-3</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.43/24</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>ACC-4</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.44/24</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Console admin Cisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>FW-1</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Interface MGMT dédiée</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.51/24</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>FW-2</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Interface MGMT dédiée</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.52/24</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0 (bridge MGMT)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.61/24</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-2</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.62/24</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-3</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.63/24</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Gateway et SVI FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Gateway VLAN 999 (VIP CARP)</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>10.254.0.254/24</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Gateway du VLAN, portée par cluster FW</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>FW-1 SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>10.254.0.253/24</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>IP physique master</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>FW-2 SVI Vlan 999</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>10.254.0.252/24</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>IP physique backup</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Scalabilité MGMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Bloc 10.254.0.0/16 = 256 /24. 1 /24 utilisé (.0). 255 /24 libres. Répartition actuelle : .1-9 Spine/Leaf, .11-19 Leaf (réserve), .21-29 Core, .31-39 Distribution, .41-49 Access, .51-59 Firewalls, .61-69 Hyperviseurs Proxmox. Possibilité d'ajouter des blocs pour storage management, OOB physique (si ajouté), bornes Wi-Fi admin, consoles IPMI, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A40:D43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1285,7 +1979,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Isolation des domaines de routage dans la fabric EVPN. AS privé 65000 (RFC 6996). RD unique par VRF (convention : AS:numéro VRF). RT import/export partagé au sein d'une VRF.</t>
+          <t>Isolation des domaines de routage dans la fabric EVPN. AS privé 65000 (RFC 6996). RD unique par VRF (convention AS:numéro de VRF). RT import/export propre à chaque VRF (aucun import croisé : l'étanchéité inter-VRF est structurelle, tout inter-VRF passe par le FW). La zone USERS (LAN) n'est pas une VRF EVPN : elle vit dans la table globale du LAN Cisco, isolée du DC par le firewall.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +2119,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>7 VLAN : outillage admin dont SOC et Vault</t>
+          <t>6 VLAN : outillage admin (CICD, observabilité, AAA, automation, Vault)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1445,37 +2139,69 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Accès contrôlé aux autres VRF via FW</t>
+          <t>Accès contrôlé aux autres VRF via FW (U-turn)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>VRF-SOC</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1 VLAN : cellule SOC (SIEM/NSM/TI/SIRP/SOAR)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>50005</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>65000:400</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>65000:400</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Sensibilité maximale ; polarité 'tout le SI → SOC' ; U-turn FW obligatoire</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>VRF-MGMT</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>1 VLAN : management in-band équipements</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>50004</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>65000:999</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>65000:999</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Sensibilité maximale, accès strict</t>
         </is>
@@ -1516,7 +2242,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Ajout potentiel d'autres VRF si le projet évolue : VRF-DEV (environnement de tests isolé), VRF-SOC (scission du SOC dans sa propre VRF pour sensibilité maximale), VRF-CLIENT-X (si passage en mode hébergement multi-tenant). La convention RT 65000:XXX laisse de la marge jusqu'à 65000:999.</t>
+          <t>Extensions futures : VRF-DEV (environnement de tests isolé si besoin d'inspection dev↔prod), VRF-INFRA (scission des services socles DNS/AD/PKI si le SI grossit), VRF-CLIENT-X (si passage en mode hébergement multi-tenant). La convention RT 65000:XXX laisse de la marge jusqu'à 65000:999.</t>
         </is>
       </c>
     </row>
@@ -1531,7 +2257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2183,7 +2909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2377,31 +3103,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Scission VRF-SOC, outillage forensics, pentest interne</t>
+          <t>Outillage forensics/DFIR, pentest interne</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>MGMT</t>
+          <t>VRF-SOC</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10.254.0.0/16</t>
+          <t>10.5.0.0/16</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
@@ -2416,6 +3142,34 @@
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Granularité SOC : SIEM/TI/SIRP/SOAR/NSM en VLAN séparés (niveau ++)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.0/16</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>OOB physique, storage management, consoles IPMI</t>
         </is>
@@ -2468,7 +3222,7 @@
       </c>
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>Créer une VRF-PREPROD avec bloc 10.5.0.0/16. Conserver la logique de segmentation PROD.</t>
+          <t>Créer une VRF-PREPROD avec bloc 10.6.0.0/16 (10.5 désormais pris par VRF-SOC). Conserver la logique de segmentation PROD.</t>
         </is>
       </c>
       <c r="C17" s="17" t="n"/>
@@ -2580,7 +3334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2687,30 +3441,38 @@
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>MGMT</t>
+          <t>DC — VRF-SOC</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>Gris (D9D9D9)</t>
+          <t>Rouge clair (FFC7CE) — cellule SOC, VRF dédiée</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Gris (D9D9D9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
           <t>Infrastructure L3</t>
         </is>
       </c>
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Jaune moutarde (FFD966)</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr"/>
-      <c r="B12" s="31" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="32" t="inlineStr">
@@ -3424,7 +4186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3884,7 +4646,7 @@
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>DC Handoff VRF — sous-interfaces 802.1Q FW ↔ Spine (16 liens logiques) — plage : 10.0.21.0/24 à 10.0.24.0/24 — protocole : Trunk 802.1Q + routage IP par VRF</t>
+          <t>DC Handoff VRF — sous-interfaces 802.1Q FW ↔ Spine (20 liens logiques) — plage : 10.0.21.0/24 (PROD) à 10.0.25.0/24 (SOC) — protocole : Trunk 802.1Q + routage IP par VRF</t>
         </is>
       </c>
     </row>
@@ -3923,12 +4685,12 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em2.201</t>
+          <t>FW-1 em2.4001</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et5.201</t>
+          <t>SPINE-1 Et5.4001</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -3948,19 +4710,19 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>VLAN 201 handoff VRF-PROD | Spine-1 .1 (VIP Anycast), FW-1 .2</t>
+          <t>VLAN 4001 handoff VRF-PROD | Spine-1 .1 (VIP Anycast), FW-1 .2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em3.201</t>
+          <t>FW-1 em3.4001</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et5.201</t>
+          <t>SPINE-2 Et5.4001</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3980,19 +4742,19 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>VLAN 201 handoff VRF-PROD | Spine-2 .5 (VIP Anycast), FW-1 .6</t>
+          <t>VLAN 4001 handoff VRF-PROD | Spine-2 .5 (VIP Anycast), FW-1 .6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em2.201</t>
+          <t>FW-2 em2.4001</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et6.201</t>
+          <t>SPINE-1 Et6.4001</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -4012,19 +4774,19 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>VLAN 201 handoff VRF-PROD | Spine-1 .9, FW-2 .10</t>
+          <t>VLAN 4001 handoff VRF-PROD | Spine-1 .9, FW-2 .10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em3.201</t>
+          <t>FW-2 em3.4001</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et6.201</t>
+          <t>SPINE-2 Et6.4001</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4044,19 +4806,19 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>VLAN 201 handoff VRF-PROD | Spine-2 .13, FW-2 .14</t>
+          <t>VLAN 4001 handoff VRF-PROD | Spine-2 .13, FW-2 .14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em2.202</t>
+          <t>FW-1 em2.4002</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et5.202</t>
+          <t>SPINE-1 Et5.4002</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -4076,19 +4838,19 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>VLAN 202 handoff VRF-DMZ</t>
+          <t>VLAN 4002 handoff VRF-DMZ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em3.202</t>
+          <t>FW-1 em3.4002</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et5.202</t>
+          <t>SPINE-2 Et5.4002</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4108,19 +4870,19 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>VLAN 202 handoff VRF-DMZ</t>
+          <t>VLAN 4002 handoff VRF-DMZ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em2.202</t>
+          <t>FW-2 em2.4002</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et6.202</t>
+          <t>SPINE-1 Et6.4002</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -4140,19 +4902,19 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>VLAN 202 handoff VRF-DMZ</t>
+          <t>VLAN 4002 handoff VRF-DMZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em3.202</t>
+          <t>FW-2 em3.4002</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et6.202</t>
+          <t>SPINE-2 Et6.4002</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4172,19 +4934,19 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>VLAN 202 handoff VRF-DMZ</t>
+          <t>VLAN 4002 handoff VRF-DMZ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em2.203</t>
+          <t>FW-1 em2.4003</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et5.203</t>
+          <t>SPINE-1 Et5.4003</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -4204,19 +4966,19 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>VLAN 203 handoff VRF-ADMIN</t>
+          <t>VLAN 4003 handoff VRF-ADMIN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em3.203</t>
+          <t>FW-1 em3.4003</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et5.203</t>
+          <t>SPINE-2 Et5.4003</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -4236,19 +4998,19 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>VLAN 203 handoff VRF-ADMIN</t>
+          <t>VLAN 4003 handoff VRF-ADMIN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em2.203</t>
+          <t>FW-2 em2.4003</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et6.203</t>
+          <t>SPINE-1 Et6.4003</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -4268,19 +5030,19 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>VLAN 203 handoff VRF-ADMIN</t>
+          <t>VLAN 4003 handoff VRF-ADMIN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em3.203</t>
+          <t>FW-2 em3.4003</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et6.203</t>
+          <t>SPINE-2 Et6.4003</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -4300,19 +5062,19 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>VLAN 203 handoff VRF-ADMIN</t>
+          <t>VLAN 4003 handoff VRF-ADMIN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em2.204</t>
+          <t>FW-1 em2.4004</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et5.204</t>
+          <t>SPINE-1 Et5.4004</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -4332,19 +5094,19 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>VLAN 204 handoff VRF-MGMT</t>
+          <t>VLAN 4004 handoff VRF-MGMT</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>FW-1 em3.204</t>
+          <t>FW-1 em3.4004</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et5.204</t>
+          <t>SPINE-2 Et5.4004</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -4364,19 +5126,19 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>VLAN 204 handoff VRF-MGMT</t>
+          <t>VLAN 4004 handoff VRF-MGMT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em2.204</t>
+          <t>FW-2 em2.4004</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>SPINE-1 Et6.204</t>
+          <t>SPINE-1 Et6.4004</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -4396,19 +5158,19 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>VLAN 204 handoff VRF-MGMT</t>
+          <t>VLAN 4004 handoff VRF-MGMT</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>FW-2 em3.204</t>
+          <t>FW-2 em3.4004</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>SPINE-2 Et6.204</t>
+          <t>SPINE-2 Et6.4004</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -4428,7 +5190,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>VLAN 204 handoff VRF-MGMT</t>
+          <t>VLAN 4004 handoff VRF-MGMT</t>
         </is>
       </c>
     </row>
@@ -4983,7 +5745,7 @@
     <row r="62" ht="85" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>Chaque VRF dispose d'un bloc /24 dédié (10.0.21.0/24 PROD, 10.0.22.0/24 DMZ, 10.0.23.0/24 ADMIN, 10.0.24.0/24 MGMT). Chaque bloc est découpé en 4 subnets /30, un par lien physique FW↔Spine. Dans chaque /30 : l'IP .1 est une VIP Anycast portée par les Spine (SPINE-1 et SPINE-2 partagent la même IP sur leurs sous-interfaces respectives d'un /30 donné, ce qui permet au FW d'envoyer indifféremment vers l'un ou l'autre Spine). Côté FW, les IP .2 (FW-1 vers Spine-1), .6 (FW-1 vers Spine-2), .10 (FW-2 vers Spine-1) et .14 (FW-2 vers Spine-2) sont des IP physiques, plus une VIP CARP par /30 sur laquelle le routage par défaut de la VRF sera pointé.</t>
+          <t>Chaque VRF dispose d'un bloc /24 dédié (10.0.21.0/24 PROD, 10.0.22.0/24 DMZ, 10.0.23.0/24 ADMIN, 10.0.24.0/24 MGMT, 10.0.25.0/24 SOC), découpé en 4 subnets /30 (un par lien physique FW↔Spine). VLAN de transit dédiés plage 4000 : 4001 PROD, 4002 DMZ, 4003 ADMIN, 4004 MGMT, 4005 SOC — jamais en collision avec les VLAN de VM. Dans chaque /30 : .1 = VIP Anycast (Spine), .2/.6/.10/.14 = IP physiques FW, plus une VIP CARP par /30 comme next-hop de la route par défaut de la VRF.</t>
         </is>
       </c>
     </row>
@@ -4991,6 +5753,173 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66"/>
+    <row r="68">
+      <c r="A68" s="36" t="inlineStr">
+        <is>
+          <t>DC Handoff VRF-SOC (ajout) — sous-interfaces 802.1Q FW ↔ Spine (4 liens) — VLAN 4005 — plage : 10.0.25.0/24 — protocole : Trunk 802.1Q + routage IP par VRF-SOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Équipement A (intf)</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Équipement B (intf)</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Préfixe</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>IP A</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>IP B</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>FW-1 em2.4005</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>SPINE-1 Et5.4005</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.0/30</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.2</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.1</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>VLAN 4005 handoff VRF-SOC | Spine-1 .1 (VIP Anycast), FW-1 .2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>FW-1 em3.4005</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>SPINE-2 Et5.4005</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.4/30</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.6</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.5</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>VLAN 4005 handoff VRF-SOC | Spine-2 .5 (VIP Anycast), FW-1 .6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>FW-2 em2.4005</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>SPINE-1 Et6.4005</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.8/30</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.10</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.9</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>VLAN 4005 handoff VRF-SOC | Spine-1 .9, FW-2 .10</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>FW-2 em3.4005</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>SPINE-2 Et6.4005</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.12/30</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.14</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>10.0.25.13</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>VLAN 4005 handoff VRF-SOC | Spine-2 .13, FW-2 .14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A46:F46"/>
@@ -6321,7 +7250,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Services infra internes (DNS, DHCP Kea, LDAP/AD, Kerberos, NTP, PKI)</t>
+          <t>Services socles internes : DNS (Unbound), DHCP (Kea), LDAP/AD (Samba), Kerberos, NTP</t>
         </is>
       </c>
     </row>
@@ -6387,7 +7316,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Mail interne et messagerie (Rocket.Chat, Mattermost)</t>
+          <t>Messagerie interne : boîtes Dovecot (IMAP/LMTP/Sieve) + webmail (SOGo/Roundcube)</t>
         </is>
       </c>
     </row>
@@ -6645,7 +7574,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>SMTP inbound MX + outbound + antispam (Rspamd)</t>
+          <t>Postfix MX inbound/outbound + Rspamd + ClamAV (anti-spam / anti-virus)</t>
         </is>
       </c>
     </row>
@@ -6760,14 +7689,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VRF-ADMIN — outillage d'administration (7 VLAN)</t>
+          <t>VRF-ADMIN — outillage d'administration (6 VLAN)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outils de gestion du SI. Séparation perf / sécu pour isoler le SIEM et les outils forensics. VLAN SOC avec politique de filtrage renforcée. VLAN Vault isolé pour la gestion des secrets.</t>
+          <t>Outils de gestion et d'exploitation du SI, segmentés par sensibilité. Le SOC a été promu dans sa propre VRF-SOC (voir onglet dédié) et ne fait plus partie de VRF-ADMIN. VLAN Vault isolé pour la gestion des secrets et la PKI interne (step-ca).</t>
         </is>
       </c>
     </row>
@@ -6903,7 +7832,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Zabbix, Prometheus, Grafana, Telegraf, collecteurs métriques</t>
+          <t>Observabilité (plan NOC) : Grafana Alloy (agents+gateway), Prometheus, Loki, Tempo, Grafana</t>
         </is>
       </c>
     </row>
@@ -6936,7 +7865,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>FreeRADIUS, Keycloak, SSO, CA interne</t>
+          <t>FreeRADIUS, Keycloak, SSO (identité et authentification centralisées)</t>
         </is>
       </c>
     </row>
@@ -7002,42 +7931,18 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>HashiCorp Vault, gestion des secrets, PKI centrale</t>
+          <t>HashiCorp Vault (secrets) + step-ca (PKI interne : émission + provisioning ACME)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n">
-        <v>306</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>ADMIN-SOC</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>10.4.36.0/24</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>10.4.36.0</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>10.4.36.255</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>10306</v>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Wazuh, Graylog, TheHive, OpenCTI, SIEM (sensibilité haute)</t>
-        </is>
-      </c>
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -7049,7 +7954,7 @@
     <row r="15" ht="50" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Le VLAN ADMIN-SOC reçoit les logs sensibles de tout le SI et stocke les investigations. Politique de filtrage : écriture (logs, télémétrie) autorisée depuis toutes les VRF, mais la lecture et l'accès admin sont restreints aux seuls analystes SOC via bastion. Dans une grande organisation, ce VLAN vivrait dans une VRF-SOC totalement distincte.</t>
+          <t>Le SOC (ex-VLAN 306) a été promu dans une VRF-SOC dédiée : le trafic de collecte suit la polarité 'tout le SI → SOC' (opposée au reste d'ADMIN, orienté 'admin → cibles'), et les données d'investigation (IOC, logs forensics) justifient une zone de confiance propre. VRF-ADMIN ne conserve que l'outillage courant (300-305).</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7970,7 @@
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>Bloc 10.4.0.0/16 = 256 /24. 7 /24 utilisés. 249 /24 libres. Extensions possibles : VLAN 307-310 pour outillage spécifique (pentest interne, DFIR, forensics), VLAN 320+ pour scission VRF-SOC dédiée si le projet grossit en ambition sécurité.</t>
+          <t>Bloc 10.4.0.0/16 = 256 /24. 6 /24 utilisés (VLAN 300-305). 250 /24 libres. Extensions : VLAN 306-310 pour outillage spécifique (DFIR, forensics, pentest interne), granularité supplémentaire par sensibilité d'outil.</t>
         </is>
       </c>
     </row>
@@ -7086,643 +7991,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VRF-MGMT — management in-band des équipements</t>
+          <t>VRF-SOC — cellule de sécurité (1 VLAN, extensible)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VLAN 999 étendu dans la fabric via VXLAN. Contient uniquement les interfaces d'administration des équipements réseau et des hyperviseurs. Aucune VM applicative ici. Accès strictement filtré depuis la VRF-ADMIN via bastion.</t>
+          <t>Zone de confiance dédiée à la supervision de sécurité, promue hors de VRF-ADMIN. Polarité de flux 'tout le SI → SOC' (collecte de logs/télémétrie) et données d'investigation à sensibilité maximale justifient une VRF propre. En standard : un VLAN unique. En niveau ++ : granularité par plan (SIEM host, NSM réseau, TI, SIRP, SOAR).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Plage réservée</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>VLAN</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Préfixe</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>IP début</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>IP fin</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>VNI L2</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Usage</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Préfixe</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>10.254.0.0/24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>IP début</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>10.254.0.0</t>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>SOC-CORE</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>10.5.0.0/24</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>10.5.0.0</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>10.5.0.255</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Wazuh (SIEM/EDR), MISP (TI), DFIR-IRIS (SIRP), Shuffle (SOAR), Malcolm (NSM) + sondes Hedgehog distribuées</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>IP fin</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>10.254.0.255</t>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Note sur la VRF-SOC</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>VLAN</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>VNI L2</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>10999</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Plan IP management</t>
-        </is>
-      </c>
-    </row>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Le SOC ingère les logs et la télémétrie de toutes les VRF (écriture autorisée depuis tout le SI vers le collecteur, jamais l'inverse) et héberge les données d'investigation (IOC, artefacts forensics). L'accès analyste se fait via bastion. L'isolation en VRF garantit qu'un compromis de l'outillage courant (VRF-ADMIN : CI/CD, monitoring perf) n'atteint pas les données SOC sans passage — et inspection — par le firewall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Équipement</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Commentaire</t>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Granularité niveau ++ (extension documentée, non déployée)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>SPINE-1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Management1 (VRF MGMT)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.1/24</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>SPINE-2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Management1</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.2/24</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Management1</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.11/24</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-2</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Management1</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.12/24</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-3</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Management1</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.13/24</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>CORE-1</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.21/24</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>CORE-2</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.22/24</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>DIST-1</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.31/24</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>DIST-2</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.32/24</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>DIST-3</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.33/24</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>DIST-4</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.34/24</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>ACC-1</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.41/24</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>ACC-2</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.42/24</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>ACC-3</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.43/24</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>ACC-4</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.44/24</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>FW-1</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Interface MGMT dédiée</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.51/24</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>FW-2</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Interface MGMT dédiée</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.52/24</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-1</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0 (bridge MGMT)</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.61/24</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-2</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.62/24</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-3</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.63/24</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Gateway et SVI FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Gateway VLAN 999 (VIP CARP)</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>10.254.0.254/24</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Gateway du VLAN, portée par cluster FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>FW-1 SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>10.254.0.253/24</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>IP physique master</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>FW-2 SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>10.254.0.252/24</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>IP physique backup</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Scalabilité MGMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>Bloc 10.254.0.0/16 = 256 /24. 1 /24 utilisé (.0). 255 /24 libres. Répartition actuelle : .1-9 Spine/Leaf, .11-19 Leaf (réserve), .21-29 Core, .31-39 Distribution, .41-49 Access, .51-59 Firewalls, .61-69 Hyperviseurs Proxmox. Possibilité d'ajouter des blocs pour storage management, OOB physique (si ajouté), bornes Wi-Fi admin, consoles IPMI, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Découpage possible en VLAN dédiés dans 10.5.0.0/16 : 401 SOC-SIEM (Wazuh), 402 SOC-NSM (Malcolm), 403 SOC-TI (MISP), 404 SOC-SIRP (DFIR-IRIS), 405 SOC-SOAR (Shuffle). RD/RT 65000:400, VNI L3 50005. Un compromis d'un plan ne donne pas accès aux autres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A40:D43"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A13:G15"/>
+    <mergeCell ref="A8:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/plan_adressage.xlsx
+++ b/plan_adressage.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-PROD" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-DMZ" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-ADMIN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-SOC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MGMT" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MGMT" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-Infra-Systeme" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VRF" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routage" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalabilité" sheetId="13" state="visible" r:id="rId13"/>
@@ -686,7 +686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Découpage hiérarchique par zone fonctionnelle, un bloc /16 par zone principale. Chaque /16 est subdivisé en /24 pour les segments broadcast et en /31 pour les liens inter-équipements. Segmentation VLAN niveau ETI (~29 VLAN totaux, cf. onglets dédiés).</t>
+          <t>Découpage hiérarchique par zone fonctionnelle, un bloc /16 par zone principale. Chaque /16 est subdivisé en /24 pour les segments broadcast et en /31 pour les liens inter-équipements. Segmentation niveau ETI : 31 VLAN de segmentation + 3 VLAN système + 4 VLAN de transit = 38 identifiants (cf. onglets dédiés).</t>
         </is>
       </c>
     </row>
@@ -769,14 +769,14 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Beaucoup de marge pour extensions fabric</t>
+          <t>Loopbacks, underlay Spine-Leaf et FW-Spine, 4 blocs de transit VRF, Core-FW, Core-Dist, pfsync</t>
         </is>
       </c>
     </row>
@@ -937,40 +937,40 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Outillage admin : CICD, observabilité, AAA, Vault, automation</t>
+          <t>Outillage admin : CICD, observabilité, AAA, Vault, automation, SOC</t>
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>SOC promu en VRF-SOC dédiée (voir bloc DC — VRF-SOC)</t>
+          <t>Inclut le VLAN 306 ADMIN-SOC, isolé par ACL sur le SVI des Leaf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>DC — VRF-SOC</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>10.5.0.0/16</t>
+          <t>10.254.0.0/16</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>10.5.0.0</t>
+          <t>10.254.0.0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>10.5.255.255</t>
+          <t>10.254.255.255</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -980,114 +980,78 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Cellule SOC (SIEM, NSM, TI, SIRP, SOAR) — VRF dédiée</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
+          <t>Management : VRF-MGMT (hyperviseurs) + segments MGMT-LAN + loopbacks d'administration L3</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>253</v>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Promu depuis ADMIN : sensibilité maximale, polarité 'tout le SI → SOC'</t>
+          <t>3 /24 : 10.254.0 (DC), 10.254.1 (LAN bloc 1), 10.254.2 (LAN bloc 2)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>WAN + bloc public simulé</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10.254.0.0/16</t>
+          <t>192.168.122.0/24</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>10.254.0.0</t>
+          <t>192.168.122.0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>10.254.255.255</t>
+          <t>192.168.122.255</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>65 536 IPs</t>
+          <t>256 IPs</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>VRF-MGMT in-band équipements (switches, FW, HV)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>255</v>
+          <t>Subnet libvirt fusionnant peering PE↔FW et bloc public (VIP CARP de services)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>1 (imposé)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Un seul /24 suffit, beaucoup de marge</t>
+          <t>Simplification lab : en prod, 2 plages distinctes (peering /30 + public /28)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>WAN + bloc public simulé</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>192.168.122.0/24</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>192.168.122.0</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>192.168.122.255</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>256 IPs</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Subnet libvirt fusionnant peering PE↔FW et bloc public (VIP CARP de services)</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>1 (imposé)</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Simplification lab : en prod, 2 plages distinctes (peering /30 + public /28)</t>
-        </is>
-      </c>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -1256,7 +1220,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>50000 + offset VRF (50001 PROD, 50002 DMZ, 50003 ADMIN, 50004 MGMT, 50005 SOC)</t>
+          <t>50000 + offset VRF (50001 PROD, 50002 DMZ, 50003 ADMIN, 50004 MGMT) — 50005 réservé pour une future VRF-SOC</t>
         </is>
       </c>
       <c r="C23" s="17" t="n"/>
@@ -1310,643 +1274,338 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VRF-MGMT — management in-band des équipements</t>
+          <t>VLAN d'infrastructure DC et VLAN système</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VLAN 999 étendu dans la fabric via VXLAN. Contient uniquement les interfaces d'administration des équipements réseau et des hyperviseurs. Aucune VM applicative ici. Accès strictement filtré depuis la VRF-ADMIN via bastion.</t>
+          <t>Deux familles de VLAN ne portent aucune machine applicative. Les VLAN d'infrastructure DC (990, 991) assurent des communications d'hyperviseur à hyperviseur et n'ont besoin d'aucun routage : privés de SVI, ils sont structurellement inatteignables depuis le reste du SI. Les VLAN système (1, 997, 998) n'existent que pour fermer des vecteurs d'attaque de niveau 2.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Plage réservée</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>VLAN</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>VNI L2</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SVI</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>VRF</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Portée</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Usage</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Préfixe</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>10.254.0.0/24</t>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>DC-CLUSTER</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>10990</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Trunks Leaf ↔ hyperviseurs</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Corosync du cluster Proxmox HV-1/HV-2 + QDevice sur HV-3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>IP début</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>10.254.0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>IP fin</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>10.254.0.255</t>
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>DC-MIGRATION</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>10991</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>aucune</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Trunks Leaf ↔ hyperviseurs</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Migration de VM et trafic de sauvegarde vers PBS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Pourquoi aucune SVI ni VRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Proxmox documente explicitement la nécessité d'un réseau distinct pour corosync. Le scénario de panne est connu : si une sauvegarde ou une migration de VM sature le lien partagé, les jetons de cluster expirent, le nœud est considéré défaillant, il est isolé et ses VM pourtant saines basculent — la panne est provoquée par le mécanisme censé l'éviter. Ces deux segments servant uniquement des échanges entre hyperviseurs tous raccordés à la même fabric, ils n'ont aucun besoin de routage. Ne pas leur attribuer de SVI produit une isolation plus robuste qu'une VRF assortie de règles, puisqu'elle ne repose sur aucune règle susceptible d'être mal écrite. PBS sera multi-homé : une patte sur le VLAN 991 pour la sauvegarde, une patte en VRF-ADMIN pour son interface d'administration. La fusion migration + sauvegarde dans un seul VLAN est une simplification volontaire : les séparer serait de la sur-conception à l'échelle de trois hyperviseurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>VLAN système — hygiène L2 (tous les switches, LAN et DC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>VLAN</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>VNI L2</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>10999</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Plan IP management</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Équipement</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Commentaire</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>SPINE-1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Management1 (VRF MGMT)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.1/24</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>SPINE-2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Management1</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.2/24</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Management1</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.11/24</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>SVI</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sur les trunks</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Ports assignés</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Portée</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Rôle</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-2</t>
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Management1</t>
+          <t>DEFAULT-UNUSED</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>10.254.0.12/24</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
+          <t>aucune</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>non — élagué</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Tous les switches</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>VLAN par défaut Cisco : conservé dans la base mais vidé de tout usage</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-3</t>
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>997</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Management1</t>
+          <t>NATIVE-UNUSED</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>10.254.0.13/24</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Arista</t>
+          <t>aucune</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>natif uniquement</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Tous les trunks</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>VLAN natif dédié : ferme le vecteur de double-encapsulation (double-tagging)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>CORE-1</t>
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>998</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>SVI Vlan 999</t>
+          <t>PARKING</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>10.254.0.21/24</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>CORE-2</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.22/24</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
+          <t>aucune</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>ports inutilisés (shutdown)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Tous les switches</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Cul-de-sac pour les ports non utilisés, filet si un port est rouvert par erreur</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>DIST-1</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.31/24</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Note sur les VLAN système</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>DIST-2</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.32/24</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>DIST-3</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.33/24</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>DIST-4</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.34/24</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>ACC-1</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.41/24</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>ACC-2</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.42/24</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>ACC-3</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.43/24</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>ACC-4</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.44/24</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Console admin Cisco</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>FW-1</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Interface MGMT dédiée</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.51/24</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>FW-2</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Interface MGMT dédiée</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.52/24</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-1</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0 (bridge MGMT)</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.61/24</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-2</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.62/24</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-3</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.63/24</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Gateway et SVI FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Gateway VLAN 999 (VIP CARP)</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>10.254.0.254/24</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Gateway du VLAN, portée par cluster FW</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>FW-1 SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>10.254.0.253/24</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>IP physique master</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>FW-2 SVI Vlan 999</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>10.254.0.252/24</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>IP physique backup</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Scalabilité MGMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>Bloc 10.254.0.0/16 = 256 /24. 1 /24 utilisé (.0). 255 /24 libres. Répartition actuelle : .1-9 Spine/Leaf, .11-19 Leaf (réserve), .21-29 Core, .31-39 Distribution, .41-49 Access, .51-59 Firewalls, .61-69 Hyperviseurs Proxmox. Possibilité d'ajouter des blocs pour storage management, OOB physique (si ajouté), bornes Wi-Fi admin, consoles IPMI, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Laisser le VLAN natif à sa valeur par défaut est l'une des non-conformités les plus systématiquement relevées en audit. L'attaque par double-encapsulation suppose que le VLAN d'accès de l'attaquant coïncide avec le VLAN natif du trunk : lui attribuer un VLAN dédié dépourvu de tout port rend cette condition impossible à réunir. La forme retenue va un cran plus loin que la recommandation minimale : le VLAN 997 est déclaré natif ET exclu de la liste des VLAN autorisés, de sorte que toute trame non étiquetée reçue sur un uplink est rejetée. Concernant le VLAN 998, le contrôle porteur reste le shutdown du port : le VLAN de parking est un filet pour le jour où un port est rouvert par un dépannage ou un script, afin qu'il n'atterrisse pas dans le VLAN 1. Les identifiants 997 et 998 sont volontairement distincts : les mutualiser recréerait, pour un port rouvert par erreur, le vecteur que le premier sert à fermer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A40:D43"/>
+  <mergeCells count="4">
+    <mergeCell ref="A21:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A9:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1979,7 +1638,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Isolation des domaines de routage dans la fabric EVPN. AS privé 65000 (RFC 6996). RD unique par VRF (convention AS:numéro de VRF). RT import/export propre à chaque VRF (aucun import croisé : l'étanchéité inter-VRF est structurelle, tout inter-VRF passe par le FW). La zone USERS (LAN) n'est pas une VRF EVPN : elle vit dans la table globale du LAN Cisco, isolée du DC par le firewall.</t>
+          <t>Isolation des domaines de routage dans la fabric EVPN. AS privé 65000 (RFC 6996). RD unique par VRF (convention AS:numéro de VRF). RT import/export propre à chaque VRF, sans aucun import croisé : l'étanchéité inter-VRF est acquise dès le plan de contrôle, avant même le firewall. Chaque VRF ne dispose que d'une route par défaut vers le FW. La zone USERS (LAN) n'est pas une VRF EVPN : elle vit dans la table globale du LAN Cisco, déjà isolée du DC par le firewall. 4 VRF déployées.</t>
         </is>
       </c>
     </row>
@@ -2119,7 +1778,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>6 VLAN : outillage admin (CICD, observabilité, AAA, automation, Vault)</t>
+          <t>7 VLAN : outillage admin (CICD, observabilité, AAA, automation, Vault, SOC)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2139,73 +1798,49 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Accès contrôlé aux autres VRF via FW (U-turn)</t>
+          <t>Accès contrôlé aux autres VRF via FW (U-turn) ; SOC isolé par ACL sur SVI Leaf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>VRF-SOC</t>
+          <t>VRF-MGMT</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>1 VLAN : cellule SOC (SIEM/NSM/TI/SIRP/SOAR)</t>
+          <t>1 VLAN : management in-band des hyperviseurs</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>50005</t>
+          <t>50004</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>65000:400</t>
+          <t>65000:999</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>65000:400</t>
+          <t>65000:999</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Sensibilité maximale ; polarité 'tout le SI → SOC' ; U-turn FW obligatoire</t>
+          <t>Sensibilité maximale, accès strict</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>VRF-MGMT</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1 VLAN : management in-band équipements</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>50004</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>65000:999</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>65000:999</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Sensibilité maximale, accès strict</t>
-        </is>
-      </c>
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -2242,7 +1877,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Extensions futures : VRF-DEV (environnement de tests isolé si besoin d'inspection dev↔prod), VRF-INFRA (scission des services socles DNS/AD/PKI si le SI grossit), VRF-CLIENT-X (si passage en mode hébergement multi-tenant). La convention RT 65000:XXX laisse de la marge jusqu'à 65000:999.</t>
+          <t>Extensions futures : VRF-SOC (promotion de la cellule SOC — identifiants réservés : 10.5.0.0/16, RD/RT 65000:400, VNI L3 50005, VLAN transit 4005, bloc de handoff 10.0.25.0/24) ; VRF-PREPROD (10.6.0.0/16) ; VRF-INFRA (scission des services socles DNS/AD si le SI grossit) ; VRF-CLIENT-X (passage en hébergement multi-tenant). La convention RT 65000:XXX laisse de la marge jusqu'à 65000:999.</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2513,7 @@
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>Une VIP VRRP par VLAN utilisateur, portée par les deux Distribution du bloc. Convention : VRID = numéro du VLAN (ex. VLAN 10 → VRID 10, VIP = .1 du subnet). Équilibrage par alternance des priorités : Dist-A master des VLAN pairs, Dist-B master des VLAN impairs. Authentification MD5 ou SHA activée.</t>
+          <t>Une VIP VRRP par VLAN utilisateur, portée par les deux Distribution du bloc. Convention : VRID = numéro du VLAN (ex. VLAN 10 → VRID 10, VIP = .1 du subnet). Équilibrage par alternance des priorités : Dist-A master des VLAN pairs, Dist-B master des VLAN impairs. Authentification MD5 ou SHA activée. Le VLAN 999 (management des switches Access) suit la même logique : VIP 10.254.1.1 sur DIST-1/DIST-2 et 10.254.2.1 sur DIST-3/DIST-4.</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2529,7 @@
     <row r="37" ht="50" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>CARP sur chaque interface data du FW (WAN, LAN, DC via VLAN VRF, MGMT). VIP partagée entre FW-1 (master, advskew=0) et FW-2 (backup, advskew=100). Synchronisation via pfsync sur le lien dédié 10.0.255.0/30 (em0 des deux FW).</t>
+          <t>CARP sur chaque interface data du FW (WAN, LAN, sous-interfaces de transit VRF vers le DC). VIP partagée entre FW-1 (master, advskew=0) et FW-2 (backup, advskew=100). Synchronisation via pfsync sur le lien dédié 10.0.255.0/30 (em0 des deux FW). Les FW n'ont plus de SVI dans le VLAN 999 : leur administration se fait via leur Loopback0 (10.0.0.41 et 10.0.0.42), annoncée en OSPF par FRR.</t>
         </is>
       </c>
     </row>
@@ -2991,14 +2626,14 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -3103,77 +2738,57 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Outillage forensics/DFIR, pentest interne</t>
+          <t>Outillage forensics/DFIR, pentest interne (VLAN 307-310)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>VRF-SOC</t>
+          <t>MGMT</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>10.5.0.0/16</t>
+          <t>10.254.0.0/16</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Granularité SOC : SIEM/TI/SIRP/SOAR/NSM en VLAN séparés (niveau ++)</t>
+          <t>Un /24 par nouveau bloc de Distribution ; OOB physique, storage management, IPMI</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>MGMT</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.0/16</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>255</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>OOB physique, storage management, consoles IPMI</t>
-        </is>
-      </c>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -3222,7 +2837,7 @@
       </c>
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>Créer une VRF-PREPROD avec bloc 10.6.0.0/16 (10.5 désormais pris par VRF-SOC). Conserver la logique de segmentation PROD.</t>
+          <t>Créer une VRF-PREPROD avec le bloc 10.6.0.0/16 (10.5.0.0/16 étant réservé à une promotion du SOC). Conserver la logique de segmentation de PROD.</t>
         </is>
       </c>
       <c r="C17" s="17" t="n"/>
@@ -3249,12 +2864,12 @@
     <row r="19" ht="35" customHeight="1">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Ajout de clients hébergés (mode MSP)</t>
+          <t>Promotion du SOC en VRF dédiée</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>Créer une VRF par client avec bloc 10.100.0.0/14 découpé par client (ex. 10.100.0.0/16 client A, 10.101.0.0/16 client B). RD 65000:XYZ. Aucun impact sur l'existant.</t>
+          <t>Déclencheurs : population d'analystes distincte des administrateurs, SOC dépassant un VLAN, ou exigence d'intégrité de la preuve opposable. Identifiants déjà réservés : 10.5.0.0/16, RD/RT 65000:400, VNI L3 50005, VLAN de transit 4005 et bloc de handoff 10.0.25.0/24. Opération bornée : renumérotation du VLAN 306 et ajout de 4 sous-interfaces par FW et par Spine.</t>
         </is>
       </c>
       <c r="C19" s="17" t="n"/>
@@ -3340,7 +2955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3441,12 +3056,12 @@
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>DC — VRF-SOC</t>
+          <t>DC — VLAN SOC</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>Rouge clair (FFC7CE) — cellule SOC, VRF dédiée</t>
+          <t>Rouge clair (FFC7CE) — VLAN 306 ADMIN-SOC, au sein de VRF-ADMIN</t>
         </is>
       </c>
     </row>
@@ -3763,6 +3378,86 @@
       <c r="B40" s="31" t="inlineStr">
         <is>
           <t>Tenir ce fichier à jour dans Git, versionner chaque modification avec date et motif.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>Conventions de numérotation complémentaires</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="inlineStr">
+        <is>
+          <t>Plage VLAN par zone</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>1xx PROD • 2xx DMZ • 3xx ADMIN • 99x infrastructure DC • 999 management • 40xx transit</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="31" t="inlineStr">
+        <is>
+          <t>VLAN de transit</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>4001 PROD, 4002 DMZ, 4003 ADMIN, 4004 MGMT — plage réservée, jamais de VM (4005 réservé SOC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="inlineStr">
+        <is>
+          <t>VLAN système</t>
+        </is>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>1 DEFAULT-UNUSED (élagué), 997 NATIVE-UNUSED (natif des trunks), 998 PARKING (ports inutilisés)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="31" t="inlineStr">
+        <is>
+          <t>VLAN d'infrastructure DC</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>990 DC-CLUSTER, 991 DC-MIGRATION — L2 purs, sans SVI ni VRF, donc non routables</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="31" t="inlineStr">
+        <is>
+          <t>Exception 3e octet ADMIN</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>3e octet = 30 + (VLAN - 300) : VLAN 300 → 10.4.30, VLAN 306 → 10.4.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="31" t="inlineStr">
+        <is>
+          <t>Administration des équipements</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>Équipements L3 : Loopback0 routée. Switches Access (L2 pur) : SVI Vlan999 du bloc.</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3796,7 +3491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Une /32 par équipement participant au routage. Sert de router-ID OSPF, source iBGP EVPN (Leaf et Spine), et VTEP Source (Leaf uniquement). Bloc réservé : 10.0.0.0/24.</t>
+          <t>Une /32 par équipement participant au routage. Sert de router-ID OSPF, de source iBGP EVPN (Leaf et Spine), de VTEP Source (Leaf uniquement) ET d'adresse d'administration in-band (SSH, syslog, SNMP et NTP sourcés sur Loopback0). Une loopback ne tombe jamais et reste joignable par le routage : c'est le point d'administration de tout équipement capable de router. Bloc réservé : 10.0.0.0/24.</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3535,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Router-ID, RR BGP EVPN</t>
+          <t>Router-ID, RR BGP EVPN, admin in-band</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3557,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Router-ID, RR BGP EVPN</t>
+          <t>Router-ID, RR BGP EVPN, admin in-band</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3579,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Router-ID, VTEP Source, client iBGP EVPN</t>
+          <t>Router-ID, VTEP Source, client iBGP EVPN, admin in-band</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3601,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Router-ID, VTEP Source, client iBGP EVPN</t>
+          <t>Router-ID, VTEP Source, client iBGP EVPN, admin in-band</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3623,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Router-ID, VTEP Source, client iBGP EVPN</t>
+          <t>Router-ID, VTEP Source, client iBGP EVPN, admin in-band</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3645,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF</t>
+          <t>Router-ID OSPF, admin in-band</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3667,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF</t>
+          <t>Router-ID OSPF, admin in-band</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3689,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF</t>
+          <t>Router-ID OSPF, admin in-band (+ SVI Vlan999 passerelle bloc 1)</t>
         </is>
       </c>
     </row>
@@ -4016,7 +3711,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF</t>
+          <t>Router-ID OSPF, admin in-band (+ SVI Vlan999 passerelle bloc 1)</t>
         </is>
       </c>
     </row>
@@ -4038,7 +3733,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF</t>
+          <t>Router-ID OSPF, admin in-band (+ SVI Vlan999 passerelle bloc 2)</t>
         </is>
       </c>
     </row>
@@ -4060,7 +3755,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF</t>
+          <t>Router-ID OSPF, admin in-band (+ SVI Vlan999 passerelle bloc 2)</t>
         </is>
       </c>
     </row>
@@ -4082,7 +3777,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF via FRR</t>
+          <t>Router-ID OSPF via FRR, admin in-band (SSH + webGUI)</t>
         </is>
       </c>
     </row>
@@ -4104,7 +3799,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Router-ID OSPF via FRR</t>
+          <t>Router-ID OSPF via FRR, admin in-band (SSH + webGUI)</t>
         </is>
       </c>
     </row>
@@ -4175,7 +3870,26 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Note — administration par loopback</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Les équipements capables de router (Spine, Leaf, Core, Distribution, FW) s'administrent via leur Loopback0, annoncée dans l'IGP. Les switches Access, purement L2, n'ont pas de loopback : ils utilisent une SVI dans le VLAN 999 de leur bloc (voir onglet MGMT). Les interfaces Management1 des Arista ne sont raccordées à aucun lien de la maquette : il n'existe pas de réseau hors-bande (OOB), simplification assumée et documentée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:D29"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4646,7 +4360,7 @@
     <row r="20">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>DC Handoff VRF — sous-interfaces 802.1Q FW ↔ Spine (20 liens logiques) — plage : 10.0.21.0/24 (PROD) à 10.0.25.0/24 (SOC) — protocole : Trunk 802.1Q + routage IP par VRF</t>
+          <t>DC Handoff VRF — sous-interfaces 802.1Q FW ↔ Spine (16 liens logiques) — plage : 10.0.21.0/24 (PROD) à 10.0.24.0/24 (MGMT) — protocole : Trunk 802.1Q + routage IP par VRF</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5459,7 @@
     <row r="62" ht="85" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>Chaque VRF dispose d'un bloc /24 dédié (10.0.21.0/24 PROD, 10.0.22.0/24 DMZ, 10.0.23.0/24 ADMIN, 10.0.24.0/24 MGMT, 10.0.25.0/24 SOC), découpé en 4 subnets /30 (un par lien physique FW↔Spine). VLAN de transit dédiés plage 4000 : 4001 PROD, 4002 DMZ, 4003 ADMIN, 4004 MGMT, 4005 SOC — jamais en collision avec les VLAN de VM. Dans chaque /30 : .1 = VIP Anycast (Spine), .2/.6/.10/.14 = IP physiques FW, plus une VIP CARP par /30 comme next-hop de la route par défaut de la VRF.</t>
+          <t>Chaque VRF dispose d'un bloc /24 dédié (10.0.21.0/24 PROD, 10.0.22.0/24 DMZ, 10.0.23.0/24 ADMIN, 10.0.24.0/24 MGMT), découpé en 4 subnets /30 (un par lien physique FW↔Spine). VLAN de transit dédiés en plage 4000 : 4001 PROD, 4002 DMZ, 4003 ADMIN, 4004 MGMT — jamais en collision avec les VLAN de VM. Dans chaque /30 : .1 = VIP Anycast (Spine), .2/.6/.10/.14 = IP physiques FW, plus une VIP CARP par /30 comme next-hop de la route par défaut de la VRF. Le bloc 10.0.25.0/24 et le VLAN 4005 sont réservés pour une éventuelle promotion du SOC en VRF dédiée.</t>
         </is>
       </c>
     </row>
@@ -5754,171 +5468,47 @@
     <row r="65"/>
     <row r="66"/>
     <row r="68">
-      <c r="A68" s="36" t="inlineStr">
-        <is>
-          <t>DC Handoff VRF-SOC (ajout) — sous-interfaces 802.1Q FW ↔ Spine (4 liens) — VLAN 4005 — plage : 10.0.25.0/24 — protocole : Trunk 802.1Q + routage IP par VRF-SOC</t>
-        </is>
-      </c>
+      <c r="A68" s="36" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Équipement A (intf)</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Équipement B (intf)</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>Préfixe</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>IP A</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>IP B</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>Commentaire</t>
-        </is>
-      </c>
+      <c r="A69" s="3" t="n"/>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n"/>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>FW-1 em2.4005</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>SPINE-1 Et5.4005</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.0/30</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.2</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.1</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>VLAN 4005 handoff VRF-SOC | Spine-1 .1 (VIP Anycast), FW-1 .2</t>
-        </is>
-      </c>
+      <c r="A70" s="7" t="n"/>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="7" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>FW-1 em3.4005</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>SPINE-2 Et5.4005</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.4/30</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.6</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.5</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>VLAN 4005 handoff VRF-SOC | Spine-2 .5 (VIP Anycast), FW-1 .6</t>
-        </is>
-      </c>
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="5" t="n"/>
+      <c r="F71" s="7" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>FW-2 em2.4005</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>SPINE-1 Et6.4005</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.8/30</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.10</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.9</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>VLAN 4005 handoff VRF-SOC | Spine-1 .9, FW-2 .10</t>
-        </is>
-      </c>
+      <c r="A72" s="7" t="n"/>
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="7" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>FW-2 em3.4005</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>SPINE-2 Et6.4005</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.12/30</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.14</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>10.0.25.13</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>VLAN 4005 handoff VRF-SOC | Spine-2 .13, FW-2 .14</t>
-        </is>
-      </c>
+      <c r="A73" s="7" t="n"/>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="5" t="n"/>
+      <c r="F73" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7689,14 +7279,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VRF-ADMIN — outillage d'administration (6 VLAN)</t>
+          <t>VRF-ADMIN — outillage d'administration (7 VLAN)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outils de gestion et d'exploitation du SI, segmentés par sensibilité. Le SOC a été promu dans sa propre VRF-SOC (voir onglet dédié) et ne fait plus partie de VRF-ADMIN. VLAN Vault isolé pour la gestion des secrets et la PKI interne (step-ca).</t>
+          <t>Outils de gestion et d'exploitation du SI, segmentés par sensibilité. La cellule SOC (VLAN 306) fait partie de cette VRF : elle est opérée par la même population et relève du même régime de privilèges — c'est la même zone de confiance. Son isolement vis-à-vis du reste de l'outillage est assuré par une ACL sur le SVI Vlan306 des Leaf. VLAN Vault isolé pour les secrets et la PKI interne (step-ca).</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7399,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ADMIN-MONITOR-PERF</t>
+          <t>ADMIN-OBSERV</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -7832,7 +7422,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Observabilité (plan NOC) : Grafana Alloy (agents+gateway), Prometheus, Loki, Tempo, Grafana</t>
+          <t>Observabilité (plan NOC) : Grafana Alloy (agents + gateway), Prometheus, Loki, Tempo, Grafana</t>
         </is>
       </c>
     </row>
@@ -7936,25 +7526,53 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="7" t="n"/>
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ADMIN-SOC</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>10.4.36.0/24</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>10.4.36.0</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>10.4.36.255</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Wazuh (SIEM/EDR), MISP (TI), DFIR-IRIS (SIRP), Shuffle (SOAR), Malcolm (NSM) + sondes Hedgehog</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Note sur le VLAN SOC</t>
+          <t>Note sur le VLAN SOC et l'arbitrage VRF-SOC</t>
         </is>
       </c>
     </row>
     <row r="15" ht="50" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Le SOC (ex-VLAN 306) a été promu dans une VRF-SOC dédiée : le trafic de collecte suit la polarité 'tout le SI → SOC' (opposée au reste d'ADMIN, orienté 'admin → cibles'), et les données d'investigation (IOC, logs forensics) justifient une zone de confiance propre. VRF-ADMIN ne conserve que l'outillage courant (300-305).</t>
+          <t>La promotion du SOC en VRF dédiée a été étudiée puis écartée. Deux arguments plaidaient pour : la polarité des flux y est inversée ('tout le SI vers le SOC' pour la collecte) et le SOC héberge les preuves d'une compromission. Trois arguments ont tranché contre : SOC et outillage d'administration relèvent de la même zone de confiance ; le coût d'une VRF pour un unique VLAN est disproportionné (L3VNI, RD/RT, 4 sous-interfaces de handoff par FW et par Spine, jeu de règles) et transforme en flux firewall tous les échanges légitimes du SOC avec Vault, l'AAA et Ansible ; enfin la promotion reste réversible à faible coût. CONTREPARTIE ASSUMÉE : les flux ADMIN vers SOC sont routés par la fabric, sans inspection firewall. COMPENSATION : ACL sur le SVI Vlan306 des Leaf n'autorisant que les ports de collecte depuis VRF-ADMIN, accès analyste réservé au bastion. Identifiants réservés pour une promotion ultérieure : 10.5.0.0/16, RD/RT 65000:400, VNI L3 50005, plage 4xx.</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7588,7 @@
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>Bloc 10.4.0.0/16 = 256 /24. 6 /24 utilisés (VLAN 300-305). 250 /24 libres. Extensions : VLAN 306-310 pour outillage spécifique (DFIR, forensics, pentest interne), granularité supplémentaire par sensibilité d'outil.</t>
+          <t>Bloc 10.4.0.0/16 = 256 /24. 7 /24 utilisés (VLAN 300-306). 249 /24 libres. CONVENTION DU 3e OCTET POUR CETTE PLAGE : 3e octet = 30 + (VLAN - 300), soit 10.4.30 pour le VLAN 300 jusqu'à 10.4.36 pour le VLAN 306, un octet ne pouvant excéder 255. Méconnaître cette exception produit des adresses invalides du type 10.4.302.10. Extensions : VLAN 307-310 pour outillage spécifique (DFIR, forensics, pentest interne). Granularité SOC niveau ++ en cas de promotion : 401 SIEM, 402 NSM, 403 TI, 404 SIRP, 405 SOAR.</t>
         </is>
       </c>
     </row>
@@ -7991,144 +7609,661 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VRF-SOC — cellule de sécurité (1 VLAN, extensible)</t>
+          <t>Management des équipements — VRF-MGMT, segments MGMT-LAN et loopbacks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Zone de confiance dédiée à la supervision de sécurité, promue hors de VRF-ADMIN. Polarité de flux 'tout le SI → SOC' (collecte de logs/télémétrie) et données d'investigation à sensibilité maximale justifient une VRF propre. En standard : un VLAN unique. En niveau ++ : granularité par plan (SIEM host, NSM réseau, TI, SIRP, SOAR).</t>
+          <t>Le management obéit à deux méthodes selon la nature de l'équipement. Les équipements capables de router (Spine, Leaf, Core, Distribution, FW) s'administrent via leur Loopback0, joignable par le routage et insensible à la perte d'un lien. Les switches Access, purement L2, utilisent une SVI dans le VLAN 999 local à leur bloc. La VRF-MGMT ne dessert donc plus que les interfaces d'administration des hyperviseurs. L'identifiant 999 est réutilisé dans trois domaines de diffusion distincts (fabric DC, bloc LAN 1, bloc LAN 2) : un numéro de VLAN n'a de portée que locale au domaine qui le porte.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Segments de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Préfixe</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>VLAN</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Préfixe</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>IP début</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>IP fin</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>VNI L2</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>SOC-CORE</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>10.5.0.0/24</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>10.5.0.0</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>10.5.0.255</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>10400</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Wazuh (SIEM/EDR), MISP (TI), DFIR-IRIS (SIRP), Shuffle (SOAR), Malcolm (NSM) + sondes Hedgehog distribuées</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Passerelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>MGMT-DC (fabric, VNI 10999)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>10.254.0.0/24</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>10.254.0.1 — anycast sur les Leaf</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Note sur la VRF-SOC</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>MGMT-LAN bloc 1 (local)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>10.254.1.0/24</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>10.254.1.1 — VIP VRRP sur DIST-1/DIST-2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Le SOC ingère les logs et la télémétrie de toutes les VRF (écriture autorisée depuis tout le SI vers le collecteur, jamais l'inverse) et héberge les données d'investigation (IOC, artefacts forensics). L'accès analyste se fait via bastion. L'isolation en VRF garantit qu'un compromis de l'outillage courant (VRF-ADMIN : CI/CD, monitoring perf) n'atteint pas les données SOC sans passage — et inspection — par le firewall.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>MGMT-LAN bloc 2 (local)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>10.254.2.0/24</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>10.254.2.1 — VIP VRRP sur DIST-3/DIST-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Loopbacks d'administration L3</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>10.0.0.0/24</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Routé via OSPF (cf. onglet Loopbacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Plan IP management</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Granularité niveau ++ (extension documentée, non déployée)</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Équipement</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>Découpage possible en VLAN dédiés dans 10.5.0.0/16 : 401 SOC-SIEM (Wazuh), 402 SOC-NSM (Malcolm), 403 SOC-TI (MISP), 404 SOC-SIRP (DFIR-IRIS), 405 SOC-SOAR (Shuffle). RD/RT 65000:400, VNI L3 50005. Un compromis d'un plan ne donne pas accès aux autres.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>SPINE-1</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.1/32</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; Management1 non câblé (pas d'OOB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>SPINE-2</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.2/32</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; Management1 non câblé (pas d'OOB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.11/32</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.12/32</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-3</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.13/32</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>CORE-1</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.21/32</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; aucun SVI de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>CORE-2</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.22/32</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; aucun SVI de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>DIST-1</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.31/32</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.1.2 (VRRP master bloc 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>DIST-2</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.32/32</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.1.3 (VRRP backup bloc 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>DIST-3</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.33/32</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.2.2 (VRRP master bloc 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>DIST-4</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.34/32</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.2.3 (VRRP backup bloc 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>FW-1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.41/32</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI ; aucune interface physique libre pour un port dédié</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>FW-2</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.42/32</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI ; aucune interface physique libre pour un port dédié</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>ACC-1</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>10.254.1.41/24</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>ACC-2</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>10.254.1.42/24</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>ACC-3</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>10.254.2.43/24</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>ACC-4</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>10.254.2.44/24</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0 (VLAN 999)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.61/24</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-2</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0 (VLAN 999)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.62/24</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-3</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0 (VLAN 999)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.63/24</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Plan interne d'un /24 de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>.1 passerelle (anycast Leaf ou VIP VRRP)  •  .2/.3 SVI Distribution A/B  •  .41-.49 switches Access  •  .61-.69 hyperviseurs  •  .100-.254 réserve</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Scalabilité et absence de réseau hors-bande</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Bloc 10.254.0.0/16 = 256 /24, dont 3 utilisés (10.254.0 fabric DC, 10.254.1 bloc LAN 1, 10.254.2 bloc LAN 2) et 253 libres. Un /24 supplémentaire par nouveau bloc de Distribution. ABSENCE D'OOB : la maquette ne comporte aucun réseau d'administration hors-bande. Les interfaces Management1 des Arista existent mais ne sont raccordées à aucun lien, et les FW n'ont plus d'interface physique disponible (em0 pfsync, em1 WAN, em2/em3 Spine, em4/em5 Core). L'administration est donc entièrement in-band. En production, on disposerait d'un réseau OOB physiquement distinct (switch dédié, IPMI/BMC, console série) pour conserver la main lorsque le plan de données est en panne. Simplification acceptable ici car l'accès console reste disponible depuis GNS3, mais limite à connaître.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A13:G15"/>
-    <mergeCell ref="A8:G10"/>
+  <mergeCells count="1">
+    <mergeCell ref="A40:D43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/plan_adressage.xlsx
+++ b/plan_adressage.xlsx
@@ -8,19 +8,20 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loopbacks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liens-L3-Infra" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WAN-et-VIP-publiques" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-LAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-PROD" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-DMZ" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-ADMIN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MGMT" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-Infra-Systeme" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VRF" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routage" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalabilité" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse-VLAN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loopbacks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liens-L3-Infra" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WAN-et-VIP-publiques" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-LAN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-PROD" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-DMZ" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-DC-ADMIN" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MGMT" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN-Infra-Systeme" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VRF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routage" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalabilité" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +71,12 @@
       <sz val="10"/>
     </font>
     <font/>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +131,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -200,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -297,6 +327,76 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1274,6 +1374,672 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Management des équipements — VRF-MGMT, segments MGMT-LAN et loopbacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Le management obéit à deux méthodes selon la nature de l'équipement. Les équipements capables de router (Spine, Leaf, Core, Distribution, FW) s'administrent via leur Loopback0, joignable par le routage et insensible à la perte d'un lien. Les switches Access, purement L2, utilisent une SVI dans le VLAN 999 local à leur bloc. La VRF-MGMT ne dessert donc plus que les interfaces d'administration des hyperviseurs. L'identifiant 999 est réutilisé dans trois domaines de diffusion distincts (fabric DC, bloc LAN 1, bloc LAN 2) : un numéro de VLAN n'a de portée que locale au domaine qui le porte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Segments de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Préfixe</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>VLAN</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Passerelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>MGMT-DC (fabric, VNI 10999)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>10.254.0.0/24</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>10.254.0.1 — anycast sur les Leaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>MGMT-LAN bloc 1 (local)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>10.254.1.0/24</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>10.254.1.1 — VIP VRRP sur DIST-1/DIST-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>MGMT-LAN bloc 2 (local)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>10.254.2.0/24</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>10.254.2.1 — VIP VRRP sur DIST-3/DIST-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Loopbacks d'administration L3</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>10.0.0.0/24</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Routé via OSPF (cf. onglet Loopbacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Plan IP management</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Équipement</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>SPINE-1</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.1/32</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; Management1 non câblé (pas d'OOB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>SPINE-2</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.2/32</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; Management1 non câblé (pas d'OOB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.11/32</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-2</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.12/32</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>LEAF-3</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.13/32</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>CORE-1</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.21/32</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; aucun SVI de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>CORE-2</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.22/32</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; aucun SVI de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>DIST-1</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.31/32</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.1.2 (VRRP master bloc 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>DIST-2</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.32/32</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.1.3 (VRRP backup bloc 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>DIST-3</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.33/32</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.2.2 (VRRP master bloc 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>DIST-4</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.34/32</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Admin in-band ; SVI Vlan999 10.254.2.3 (VRRP backup bloc 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>FW-1</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.41/32</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI ; aucune interface physique libre pour un port dédié</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>FW-2</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Loopback0</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>10.0.0.42/32</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI ; aucune interface physique libre pour un port dédié</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>ACC-1</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>10.254.1.41/24</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>ACC-2</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>10.254.1.42/24</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>ACC-3</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>10.254.2.43/24</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>ACC-4</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>SVI Vlan999</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>10.254.2.44/24</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>L2 pur ; ip default-gateway 10.254.2.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-1</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0 (VLAN 999)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.61/24</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-2</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0 (VLAN 999)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.62/24</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>ProxmoxVE-3</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>vmbr0 (VLAN 999)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>10.254.0.63/24</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Plan interne d'un /24 de management</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>.1 passerelle (anycast Leaf ou VIP VRRP)  •  .2/.3 SVI Distribution A/B  •  .41-.49 switches Access  •  .61-.69 hyperviseurs  •  .100-.254 réserve</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr"/>
+      <c r="C35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Scalabilité et absence de réseau hors-bande</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Bloc 10.254.0.0/16 = 256 /24, dont 3 utilisés (10.254.0 fabric DC, 10.254.1 bloc LAN 1, 10.254.2 bloc LAN 2) et 253 libres. Un /24 supplémentaire par nouveau bloc de Distribution. ABSENCE D'OOB : la maquette ne comporte aucun réseau d'administration hors-bande. Les interfaces Management1 des Arista existent mais ne sont raccordées à aucun lien, et les FW n'ont plus d'interface physique disponible (em0 pfsync, em1 WAN, em2/em3 Spine, em4/em5 Core). L'administration est donc entièrement in-band. En production, on disposerait d'un réseau OOB physiquement distinct (switch dédié, IPMI/BMC, console série) pour conserver la main lorsque le plan de données est en panne. Simplification acceptable ici car l'accès console reste disponible depuis GNS3, mais limite à connaître.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A40:D43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1611,7 +2377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1892,7 +2658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2544,7 +3310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2949,7 +3715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3467,6 +4233,1969 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Synthèse consolidée du plan VLAN / VNI / VRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>Vue unique de tous les segments, triés par zone de confiance. Conventions : VNI L2 = 10000 + n° VLAN · VNI L3 = 50000 + offset VRF · RD/RT = 65000:n° VRF · un /16 par zone, un /24 par VLAN. USERS = table globale LAN (pas une VRF EVPN, donc ni VNI ni RD/RT). 4 VRF EVPN déployées.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>VRF / Zone</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>VLAN</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sous-réseau (CIDR)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>IP début</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>IP fin</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>VNI L2</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>VNI L3</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>RD / RT</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="inlineStr">
+        <is>
+          <t>10.1.10.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E5" s="42" t="inlineStr">
+        <is>
+          <t>10.1.10.0</t>
+        </is>
+      </c>
+      <c r="F5" s="42" t="inlineStr">
+        <is>
+          <t>10.1.10.255</t>
+        </is>
+      </c>
+      <c r="G5" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="44" t="inlineStr">
+        <is>
+          <t>Postes bureautiques — cœur du LAN (bloc 2 = +100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>VOICE</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>10.1.20.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>10.1.20.0</t>
+        </is>
+      </c>
+      <c r="F6" s="42" t="inlineStr">
+        <is>
+          <t>10.1.20.255</t>
+        </is>
+      </c>
+      <c r="G6" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="44" t="inlineStr">
+        <is>
+          <t>ToIP : voice VLAN sur ports access, QoS dédiée</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" s="42" t="inlineStr">
+        <is>
+          <t>IOT</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>10.1.30.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E7" s="42" t="inlineStr">
+        <is>
+          <t>10.1.30.0</t>
+        </is>
+      </c>
+      <c r="F7" s="42" t="inlineStr">
+        <is>
+          <t>10.1.30.255</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="44" t="inlineStr">
+        <is>
+          <t>Caméras, capteurs, IoT — isolement strict</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B8" s="43" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>WIFI-CORP</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>10.1.40.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t>10.1.40.0</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>10.1.40.255</t>
+        </is>
+      </c>
+      <c r="G8" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="44" t="inlineStr">
+        <is>
+          <t>Wi-Fi salariés WPA3-Enterprise + RADIUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
+        <is>
+          <t>WIFI-GUEST</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>10.1.41.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E9" s="42" t="inlineStr">
+        <is>
+          <t>10.1.41.0</t>
+        </is>
+      </c>
+      <c r="F9" s="42" t="inlineStr">
+        <is>
+          <t>10.1.41.255</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="44" t="inlineStr">
+        <is>
+          <t>Invités — Internet uniquement, aucun accès interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>WIFI-BYOD</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>10.1.42.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E10" s="42" t="inlineStr">
+        <is>
+          <t>10.1.42.0</t>
+        </is>
+      </c>
+      <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>10.1.42.255</t>
+        </is>
+      </c>
+      <c r="G10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="44" t="inlineStr">
+        <is>
+          <t>Terminaux personnels — accès restreint</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" s="42" t="inlineStr">
+        <is>
+          <t>PRINTERS</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="inlineStr">
+        <is>
+          <t>10.1.50.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="inlineStr">
+        <is>
+          <t>10.1.50.0</t>
+        </is>
+      </c>
+      <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>10.1.50.255</t>
+        </is>
+      </c>
+      <c r="G11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="44" t="inlineStr">
+        <is>
+          <t>Imprimantes / MFP — isolement fort</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>USERS</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="n">
+        <v>90</v>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>LAB-DEV</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>10.1.90.0/24 ×2</t>
+        </is>
+      </c>
+      <c r="E12" s="42" t="inlineStr">
+        <is>
+          <t>10.1.90.0</t>
+        </is>
+      </c>
+      <c r="F12" s="42" t="inlineStr">
+        <is>
+          <t>10.1.90.255</t>
+        </is>
+      </c>
+      <c r="G12" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="44" t="inlineStr">
+        <is>
+          <t>Postes de développement et bancs de test (endpoints)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" s="45" t="inlineStr">
+        <is>
+          <t>PROD-WEB-INT</t>
+        </is>
+      </c>
+      <c r="D13" s="45" t="inlineStr">
+        <is>
+          <t>10.2.100.0/24</t>
+        </is>
+      </c>
+      <c r="E13" s="45" t="inlineStr">
+        <is>
+          <t>10.2.100.0</t>
+        </is>
+      </c>
+      <c r="F13" s="45" t="inlineStr">
+        <is>
+          <t>10.2.100.255</t>
+        </is>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>10100</v>
+      </c>
+      <c r="H13" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I13" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J13" s="47" t="inlineStr">
+        <is>
+          <t>Tier présentation (3-tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B14" s="46" t="n">
+        <v>101</v>
+      </c>
+      <c r="C14" s="45" t="inlineStr">
+        <is>
+          <t>PROD-APP</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="inlineStr">
+        <is>
+          <t>10.2.101.0/24</t>
+        </is>
+      </c>
+      <c r="E14" s="45" t="inlineStr">
+        <is>
+          <t>10.2.101.0</t>
+        </is>
+      </c>
+      <c r="F14" s="45" t="inlineStr">
+        <is>
+          <t>10.2.101.255</t>
+        </is>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>10101</v>
+      </c>
+      <c r="H14" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I14" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J14" s="47" t="inlineStr">
+        <is>
+          <t>Tier applicatif (backends, ERP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B15" s="46" t="n">
+        <v>102</v>
+      </c>
+      <c r="C15" s="45" t="inlineStr">
+        <is>
+          <t>PROD-DB</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="inlineStr">
+        <is>
+          <t>10.2.102.0/24</t>
+        </is>
+      </c>
+      <c r="E15" s="45" t="inlineStr">
+        <is>
+          <t>10.2.102.0</t>
+        </is>
+      </c>
+      <c r="F15" s="45" t="inlineStr">
+        <is>
+          <t>10.2.102.255</t>
+        </is>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>10102</v>
+      </c>
+      <c r="H15" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I15" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J15" s="47" t="inlineStr">
+        <is>
+          <t>Tier données — jamais exposé en DMZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="n">
+        <v>103</v>
+      </c>
+      <c r="C16" s="45" t="inlineStr">
+        <is>
+          <t>PROD-INFRA</t>
+        </is>
+      </c>
+      <c r="D16" s="45" t="inlineStr">
+        <is>
+          <t>10.2.103.0/24</t>
+        </is>
+      </c>
+      <c r="E16" s="45" t="inlineStr">
+        <is>
+          <t>10.2.103.0</t>
+        </is>
+      </c>
+      <c r="F16" s="45" t="inlineStr">
+        <is>
+          <t>10.2.103.255</t>
+        </is>
+      </c>
+      <c r="G16" s="46" t="n">
+        <v>10103</v>
+      </c>
+      <c r="H16" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I16" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J16" s="47" t="inlineStr">
+        <is>
+          <t>Services socles : DNS, DHCP, LDAP/AD, Kerberos, NTP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="n">
+        <v>104</v>
+      </c>
+      <c r="C17" s="45" t="inlineStr">
+        <is>
+          <t>PROD-FILES</t>
+        </is>
+      </c>
+      <c r="D17" s="45" t="inlineStr">
+        <is>
+          <t>10.2.104.0/24</t>
+        </is>
+      </c>
+      <c r="E17" s="45" t="inlineStr">
+        <is>
+          <t>10.2.104.0</t>
+        </is>
+      </c>
+      <c r="F17" s="45" t="inlineStr">
+        <is>
+          <t>10.2.104.255</t>
+        </is>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>10104</v>
+      </c>
+      <c r="H17" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I17" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J17" s="47" t="inlineStr">
+        <is>
+          <t>Partages de fichiers (NextCloud, SMB, NFS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="n">
+        <v>105</v>
+      </c>
+      <c r="C18" s="45" t="inlineStr">
+        <is>
+          <t>PROD-MESSAGING</t>
+        </is>
+      </c>
+      <c r="D18" s="45" t="inlineStr">
+        <is>
+          <t>10.2.105.0/24</t>
+        </is>
+      </c>
+      <c r="E18" s="45" t="inlineStr">
+        <is>
+          <t>10.2.105.0</t>
+        </is>
+      </c>
+      <c r="F18" s="45" t="inlineStr">
+        <is>
+          <t>10.2.105.255</t>
+        </is>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>10105</v>
+      </c>
+      <c r="H18" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I18" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J18" s="47" t="inlineStr">
+        <is>
+          <t>Boîtes Dovecot + webmail interne</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="n">
+        <v>106</v>
+      </c>
+      <c r="C19" s="45" t="inlineStr">
+        <is>
+          <t>PROD-TOIP</t>
+        </is>
+      </c>
+      <c r="D19" s="45" t="inlineStr">
+        <is>
+          <t>10.2.106.0/24</t>
+        </is>
+      </c>
+      <c r="E19" s="45" t="inlineStr">
+        <is>
+          <t>10.2.106.0</t>
+        </is>
+      </c>
+      <c r="F19" s="45" t="inlineStr">
+        <is>
+          <t>10.2.106.255</t>
+        </is>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>10106</v>
+      </c>
+      <c r="H19" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I19" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J19" s="47" t="inlineStr">
+        <is>
+          <t>Backend ToIP (Asterisk, SIP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n">
+        <v>107</v>
+      </c>
+      <c r="C20" s="45" t="inlineStr">
+        <is>
+          <t>PROD-INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D20" s="45" t="inlineStr">
+        <is>
+          <t>10.2.107.0/24</t>
+        </is>
+      </c>
+      <c r="E20" s="45" t="inlineStr">
+        <is>
+          <t>10.2.107.0</t>
+        </is>
+      </c>
+      <c r="F20" s="45" t="inlineStr">
+        <is>
+          <t>10.2.107.255</t>
+        </is>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>10107</v>
+      </c>
+      <c r="H20" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I20" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J20" s="47" t="inlineStr">
+        <is>
+          <t>Brokers de messages (Kafka, RabbitMQ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>VRF-DMZ</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="n">
+        <v>200</v>
+      </c>
+      <c r="C21" s="48" t="inlineStr">
+        <is>
+          <t>DMZ-FRONT</t>
+        </is>
+      </c>
+      <c r="D21" s="48" t="inlineStr">
+        <is>
+          <t>10.3.200.0/24</t>
+        </is>
+      </c>
+      <c r="E21" s="48" t="inlineStr">
+        <is>
+          <t>10.3.200.0</t>
+        </is>
+      </c>
+      <c r="F21" s="48" t="inlineStr">
+        <is>
+          <t>10.3.200.255</t>
+        </is>
+      </c>
+      <c r="G21" s="49" t="n">
+        <v>10200</v>
+      </c>
+      <c r="H21" s="49" t="n">
+        <v>50002</v>
+      </c>
+      <c r="I21" s="48" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="J21" s="50" t="inlineStr">
+        <is>
+          <t>Reverse proxy + WAF — point d'entrée exposé</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>VRF-DMZ</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="n">
+        <v>201</v>
+      </c>
+      <c r="C22" s="48" t="inlineStr">
+        <is>
+          <t>DMZ-WEB</t>
+        </is>
+      </c>
+      <c r="D22" s="48" t="inlineStr">
+        <is>
+          <t>10.3.201.0/24</t>
+        </is>
+      </c>
+      <c r="E22" s="48" t="inlineStr">
+        <is>
+          <t>10.3.201.0</t>
+        </is>
+      </c>
+      <c r="F22" s="48" t="inlineStr">
+        <is>
+          <t>10.3.201.255</t>
+        </is>
+      </c>
+      <c r="G22" s="49" t="n">
+        <v>10201</v>
+      </c>
+      <c r="H22" s="49" t="n">
+        <v>50002</v>
+      </c>
+      <c r="I22" s="48" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="J22" s="50" t="inlineStr">
+        <is>
+          <t>Serveurs web exposés</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>VRF-DMZ</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="n">
+        <v>202</v>
+      </c>
+      <c r="C23" s="48" t="inlineStr">
+        <is>
+          <t>DMZ-MAIL</t>
+        </is>
+      </c>
+      <c r="D23" s="48" t="inlineStr">
+        <is>
+          <t>10.3.202.0/24</t>
+        </is>
+      </c>
+      <c r="E23" s="48" t="inlineStr">
+        <is>
+          <t>10.3.202.0</t>
+        </is>
+      </c>
+      <c r="F23" s="48" t="inlineStr">
+        <is>
+          <t>10.3.202.255</t>
+        </is>
+      </c>
+      <c r="G23" s="49" t="n">
+        <v>10202</v>
+      </c>
+      <c r="H23" s="49" t="n">
+        <v>50002</v>
+      </c>
+      <c r="I23" s="48" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="J23" s="50" t="inlineStr">
+        <is>
+          <t>MX Postfix + Rspamd + ClamAV</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>VRF-DMZ</t>
+        </is>
+      </c>
+      <c r="B24" s="49" t="n">
+        <v>203</v>
+      </c>
+      <c r="C24" s="48" t="inlineStr">
+        <is>
+          <t>DMZ-DNS</t>
+        </is>
+      </c>
+      <c r="D24" s="48" t="inlineStr">
+        <is>
+          <t>10.3.203.0/24</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>10.3.203.0</t>
+        </is>
+      </c>
+      <c r="F24" s="48" t="inlineStr">
+        <is>
+          <t>10.3.203.255</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="n">
+        <v>10203</v>
+      </c>
+      <c r="H24" s="49" t="n">
+        <v>50002</v>
+      </c>
+      <c r="I24" s="48" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="J24" s="50" t="inlineStr">
+        <is>
+          <t>DNS autoritaire public</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>VRF-DMZ</t>
+        </is>
+      </c>
+      <c r="B25" s="49" t="n">
+        <v>204</v>
+      </c>
+      <c r="C25" s="48" t="inlineStr">
+        <is>
+          <t>DMZ-API</t>
+        </is>
+      </c>
+      <c r="D25" s="48" t="inlineStr">
+        <is>
+          <t>10.3.204.0/24</t>
+        </is>
+      </c>
+      <c r="E25" s="48" t="inlineStr">
+        <is>
+          <t>10.3.204.0</t>
+        </is>
+      </c>
+      <c r="F25" s="48" t="inlineStr">
+        <is>
+          <t>10.3.204.255</t>
+        </is>
+      </c>
+      <c r="G25" s="49" t="n">
+        <v>10204</v>
+      </c>
+      <c r="H25" s="49" t="n">
+        <v>50002</v>
+      </c>
+      <c r="I25" s="48" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="J25" s="50" t="inlineStr">
+        <is>
+          <t>Passerelle d'API publiques</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B26" s="52" t="n">
+        <v>300</v>
+      </c>
+      <c r="C26" s="51" t="inlineStr">
+        <is>
+          <t>ADMIN-CORE</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="inlineStr">
+        <is>
+          <t>10.4.30.0/24</t>
+        </is>
+      </c>
+      <c r="E26" s="51" t="inlineStr">
+        <is>
+          <t>10.4.30.0</t>
+        </is>
+      </c>
+      <c r="F26" s="51" t="inlineStr">
+        <is>
+          <t>10.4.30.255</t>
+        </is>
+      </c>
+      <c r="G26" s="52" t="n">
+        <v>10300</v>
+      </c>
+      <c r="H26" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I26" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J26" s="53" t="inlineStr">
+        <is>
+          <t>Bastion, PBS, GLPI — accès d'administration</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B27" s="52" t="n">
+        <v>301</v>
+      </c>
+      <c r="C27" s="51" t="inlineStr">
+        <is>
+          <t>ADMIN-CICD</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="inlineStr">
+        <is>
+          <t>10.4.31.0/24</t>
+        </is>
+      </c>
+      <c r="E27" s="51" t="inlineStr">
+        <is>
+          <t>10.4.31.0</t>
+        </is>
+      </c>
+      <c r="F27" s="51" t="inlineStr">
+        <is>
+          <t>10.4.31.255</t>
+        </is>
+      </c>
+      <c r="G27" s="52" t="n">
+        <v>10301</v>
+      </c>
+      <c r="H27" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I27" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J27" s="53" t="inlineStr">
+        <is>
+          <t>CI/CD (GitLab, runners) — vecteur isolé</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B28" s="52" t="n">
+        <v>302</v>
+      </c>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>ADMIN-OBSERV</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="inlineStr">
+        <is>
+          <t>10.4.32.0/24</t>
+        </is>
+      </c>
+      <c r="E28" s="51" t="inlineStr">
+        <is>
+          <t>10.4.32.0</t>
+        </is>
+      </c>
+      <c r="F28" s="51" t="inlineStr">
+        <is>
+          <t>10.4.32.255</t>
+        </is>
+      </c>
+      <c r="G28" s="52" t="n">
+        <v>10302</v>
+      </c>
+      <c r="H28" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I28" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J28" s="53" t="inlineStr">
+        <is>
+          <t>Observabilité (Alloy, Prometheus, Loki, Tempo, Grafana)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B29" s="52" t="n">
+        <v>303</v>
+      </c>
+      <c r="C29" s="51" t="inlineStr">
+        <is>
+          <t>ADMIN-AAA</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="inlineStr">
+        <is>
+          <t>10.4.33.0/24</t>
+        </is>
+      </c>
+      <c r="E29" s="51" t="inlineStr">
+        <is>
+          <t>10.4.33.0</t>
+        </is>
+      </c>
+      <c r="F29" s="51" t="inlineStr">
+        <is>
+          <t>10.4.33.255</t>
+        </is>
+      </c>
+      <c r="G29" s="52" t="n">
+        <v>10303</v>
+      </c>
+      <c r="H29" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I29" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J29" s="53" t="inlineStr">
+        <is>
+          <t>Identité centralisée (FreeRADIUS, Keycloak, SSO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n">
+        <v>304</v>
+      </c>
+      <c r="C30" s="51" t="inlineStr">
+        <is>
+          <t>ADMIN-AUTOMATE</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="inlineStr">
+        <is>
+          <t>10.4.34.0/24</t>
+        </is>
+      </c>
+      <c r="E30" s="51" t="inlineStr">
+        <is>
+          <t>10.4.34.0</t>
+        </is>
+      </c>
+      <c r="F30" s="51" t="inlineStr">
+        <is>
+          <t>10.4.34.255</t>
+        </is>
+      </c>
+      <c r="G30" s="52" t="n">
+        <v>10304</v>
+      </c>
+      <c r="H30" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I30" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>Ansible, AWX — portée destructrice, isolé</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n">
+        <v>305</v>
+      </c>
+      <c r="C31" s="51" t="inlineStr">
+        <is>
+          <t>ADMIN-VAULT</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="inlineStr">
+        <is>
+          <t>10.4.35.0/24</t>
+        </is>
+      </c>
+      <c r="E31" s="51" t="inlineStr">
+        <is>
+          <t>10.4.35.0</t>
+        </is>
+      </c>
+      <c r="F31" s="51" t="inlineStr">
+        <is>
+          <t>10.4.35.255</t>
+        </is>
+      </c>
+      <c r="G31" s="52" t="n">
+        <v>10305</v>
+      </c>
+      <c r="H31" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I31" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J31" s="53" t="inlineStr">
+        <is>
+          <t>Vault + step-ca (PKI) — sensibilité maximale</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n">
+        <v>306</v>
+      </c>
+      <c r="C32" s="51" t="inlineStr">
+        <is>
+          <t>ADMIN-SOC</t>
+        </is>
+      </c>
+      <c r="D32" s="51" t="inlineStr">
+        <is>
+          <t>10.4.36.0/24</t>
+        </is>
+      </c>
+      <c r="E32" s="51" t="inlineStr">
+        <is>
+          <t>10.4.36.0</t>
+        </is>
+      </c>
+      <c r="F32" s="51" t="inlineStr">
+        <is>
+          <t>10.4.36.255</t>
+        </is>
+      </c>
+      <c r="G32" s="52" t="n">
+        <v>10306</v>
+      </c>
+      <c r="H32" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I32" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J32" s="53" t="inlineStr">
+        <is>
+          <t>SIEM/NSM/TI/SIRP/SOAR — isolé par ACL sur SVI Leaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="54" t="inlineStr">
+        <is>
+          <t>VRF-MGMT</t>
+        </is>
+      </c>
+      <c r="B33" s="55" t="n">
+        <v>999</v>
+      </c>
+      <c r="C33" s="54" t="inlineStr">
+        <is>
+          <t>MGMT-DC</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>10.254.0.0/24</t>
+        </is>
+      </c>
+      <c r="E33" s="54" t="inlineStr">
+        <is>
+          <t>10.254.0.0</t>
+        </is>
+      </c>
+      <c r="F33" s="54" t="inlineStr">
+        <is>
+          <t>10.254.0.255</t>
+        </is>
+      </c>
+      <c r="G33" s="55" t="n">
+        <v>10999</v>
+      </c>
+      <c r="H33" s="55" t="n">
+        <v>50004</v>
+      </c>
+      <c r="I33" s="54" t="inlineStr">
+        <is>
+          <t>65000:999</t>
+        </is>
+      </c>
+      <c r="J33" s="56" t="inlineStr">
+        <is>
+          <t>Admin des hyperviseurs — anycast sur les Leaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="54" t="inlineStr">
+        <is>
+          <t>LAN-global</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="n">
+        <v>999</v>
+      </c>
+      <c r="C34" s="54" t="inlineStr">
+        <is>
+          <t>MGMT-LAN</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>10.254.1.0/24 · .2</t>
+        </is>
+      </c>
+      <c r="E34" s="54" t="inlineStr">
+        <is>
+          <t>10.254.1.0</t>
+        </is>
+      </c>
+      <c r="F34" s="54" t="inlineStr">
+        <is>
+          <t>10.254.2.255</t>
+        </is>
+      </c>
+      <c r="G34" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="56" t="inlineStr">
+        <is>
+          <t>Admin des switches Access — VIP VRRP sur Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="57" t="inlineStr">
+        <is>
+          <t>(aucune)</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="n">
+        <v>990</v>
+      </c>
+      <c r="C35" s="57" t="inlineStr">
+        <is>
+          <t>DC-CLUSTER</t>
+        </is>
+      </c>
+      <c r="D35" s="57" t="inlineStr">
+        <is>
+          <t>— (L2 pur)</t>
+        </is>
+      </c>
+      <c r="E35" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="58" t="n">
+        <v>10990</v>
+      </c>
+      <c r="H35" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="59" t="inlineStr">
+        <is>
+          <t>Corosync du cluster Proxmox — non routable (reco Proxmox)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="57" t="inlineStr">
+        <is>
+          <t>(aucune)</t>
+        </is>
+      </c>
+      <c r="B36" s="58" t="n">
+        <v>991</v>
+      </c>
+      <c r="C36" s="57" t="inlineStr">
+        <is>
+          <t>DC-MIGRATION</t>
+        </is>
+      </c>
+      <c r="D36" s="57" t="inlineStr">
+        <is>
+          <t>— (L2 pur)</t>
+        </is>
+      </c>
+      <c r="E36" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="58" t="n">
+        <v>10991</v>
+      </c>
+      <c r="H36" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="59" t="inlineStr">
+        <is>
+          <t>Migration de VM + sauvegarde PBS — non routable</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="60" t="inlineStr">
+        <is>
+          <t>(système)</t>
+        </is>
+      </c>
+      <c r="B37" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="60" t="inlineStr">
+        <is>
+          <t>DEFAULT-UNUSED</t>
+        </is>
+      </c>
+      <c r="D37" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="62" t="inlineStr">
+        <is>
+          <t>VLAN 1 vidé de tout usage (durcissement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="60" t="inlineStr">
+        <is>
+          <t>(système)</t>
+        </is>
+      </c>
+      <c r="B38" s="61" t="n">
+        <v>997</v>
+      </c>
+      <c r="C38" s="60" t="inlineStr">
+        <is>
+          <t>NATIVE-UNUSED</t>
+        </is>
+      </c>
+      <c r="D38" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="62" t="inlineStr">
+        <is>
+          <t>Natif dédié des trunks — anti double-tagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>(système)</t>
+        </is>
+      </c>
+      <c r="B39" s="61" t="n">
+        <v>998</v>
+      </c>
+      <c r="C39" s="60" t="inlineStr">
+        <is>
+          <t>PARKING</t>
+        </is>
+      </c>
+      <c r="D39" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="62" t="inlineStr">
+        <is>
+          <t>Ports inutilisés (shutdown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="45" t="inlineStr">
+        <is>
+          <t>VRF-PROD</t>
+        </is>
+      </c>
+      <c r="B40" s="46" t="n">
+        <v>4001</v>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>TRANSIT-PROD</t>
+        </is>
+      </c>
+      <c r="D40" s="45" t="inlineStr">
+        <is>
+          <t>10.0.21.0/24</t>
+        </is>
+      </c>
+      <c r="E40" s="45" t="inlineStr">
+        <is>
+          <t>10.0.21.0</t>
+        </is>
+      </c>
+      <c r="F40" s="45" t="inlineStr">
+        <is>
+          <t>10.0.21.255</t>
+        </is>
+      </c>
+      <c r="G40" s="46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="46" t="n">
+        <v>50001</v>
+      </c>
+      <c r="I40" s="45" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="J40" s="47" t="inlineStr">
+        <is>
+          <t>Handoff VRF-PROD ↔ FW (4 × /30, sans hôte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="48" t="inlineStr">
+        <is>
+          <t>VRF-DMZ</t>
+        </is>
+      </c>
+      <c r="B41" s="49" t="n">
+        <v>4002</v>
+      </c>
+      <c r="C41" s="48" t="inlineStr">
+        <is>
+          <t>TRANSIT-DMZ</t>
+        </is>
+      </c>
+      <c r="D41" s="48" t="inlineStr">
+        <is>
+          <t>10.0.22.0/24</t>
+        </is>
+      </c>
+      <c r="E41" s="48" t="inlineStr">
+        <is>
+          <t>10.0.22.0</t>
+        </is>
+      </c>
+      <c r="F41" s="48" t="inlineStr">
+        <is>
+          <t>10.0.22.255</t>
+        </is>
+      </c>
+      <c r="G41" s="49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="49" t="n">
+        <v>50002</v>
+      </c>
+      <c r="I41" s="48" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="J41" s="50" t="inlineStr">
+        <is>
+          <t>Handoff VRF-DMZ ↔ FW (4 × /30, sans hôte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="51" t="inlineStr">
+        <is>
+          <t>VRF-ADMIN</t>
+        </is>
+      </c>
+      <c r="B42" s="52" t="n">
+        <v>4003</v>
+      </c>
+      <c r="C42" s="51" t="inlineStr">
+        <is>
+          <t>TRANSIT-ADMIN</t>
+        </is>
+      </c>
+      <c r="D42" s="51" t="inlineStr">
+        <is>
+          <t>10.0.23.0/24</t>
+        </is>
+      </c>
+      <c r="E42" s="51" t="inlineStr">
+        <is>
+          <t>10.0.23.0</t>
+        </is>
+      </c>
+      <c r="F42" s="51" t="inlineStr">
+        <is>
+          <t>10.0.23.255</t>
+        </is>
+      </c>
+      <c r="G42" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="52" t="n">
+        <v>50003</v>
+      </c>
+      <c r="I42" s="51" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="J42" s="53" t="inlineStr">
+        <is>
+          <t>Handoff VRF-ADMIN ↔ FW (4 × /30, sans hôte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="54" t="inlineStr">
+        <is>
+          <t>VRF-MGMT</t>
+        </is>
+      </c>
+      <c r="B43" s="55" t="n">
+        <v>4004</v>
+      </c>
+      <c r="C43" s="54" t="inlineStr">
+        <is>
+          <t>TRANSIT-MGMT</t>
+        </is>
+      </c>
+      <c r="D43" s="54" t="inlineStr">
+        <is>
+          <t>10.0.24.0/24</t>
+        </is>
+      </c>
+      <c r="E43" s="54" t="inlineStr">
+        <is>
+          <t>10.0.24.0</t>
+        </is>
+      </c>
+      <c r="F43" s="54" t="inlineStr">
+        <is>
+          <t>10.0.24.255</t>
+        </is>
+      </c>
+      <c r="G43" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="55" t="n">
+        <v>50004</v>
+      </c>
+      <c r="I43" s="54" t="inlineStr">
+        <is>
+          <t>65000:999</t>
+        </is>
+      </c>
+      <c r="J43" s="56" t="inlineStr">
+        <is>
+          <t>Handoff VRF-MGMT ↔ FW (4 × /30, sans hôte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="63" t="inlineStr">
+        <is>
+          <t>Décompte</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>38 identifiants : 31 de segmentation (8 USERS + 8 PROD + 5 DMZ + 7 ADMIN + 1 MGMT + 2 infra DC) + 3 système + 4 transit. 4 VRF EVPN. Aucun chevauchement, aucun import RT croisé.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C45:J45"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3894,7 +6623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5524,7 +8253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6050,7 +8779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6643,13 +9372,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6658,7 +9387,9 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6708,6 +9439,16 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>VNI L3</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RD / RT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Usage</t>
         </is>
       </c>
@@ -6739,7 +9480,15 @@
       <c r="F5" s="5" t="n">
         <v>10100</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I5" s="40" t="inlineStr">
         <is>
           <t>Frontaux web internes (intranet, portails applicatifs)</t>
         </is>
@@ -6772,7 +9521,15 @@
       <c r="F6" s="5" t="n">
         <v>10101</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I6" s="40" t="inlineStr">
         <is>
           <t>Serveurs applicatifs métier (backends, ERP, logique métier)</t>
         </is>
@@ -6805,7 +9562,15 @@
       <c r="F7" s="5" t="n">
         <v>10102</v>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I7" s="40" t="inlineStr">
         <is>
           <t>Bases de données (PostgreSQL, MariaDB, MongoDB)</t>
         </is>
@@ -6838,7 +9603,15 @@
       <c r="F8" s="5" t="n">
         <v>10103</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I8" s="40" t="inlineStr">
         <is>
           <t>Services socles internes : DNS (Unbound), DHCP (Kea), LDAP/AD (Samba), Kerberos, NTP</t>
         </is>
@@ -6871,7 +9644,15 @@
       <c r="F9" s="5" t="n">
         <v>10104</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I9" s="40" t="inlineStr">
         <is>
           <t>Partages de fichiers (NextCloud, SMB, NFS)</t>
         </is>
@@ -6904,7 +9685,15 @@
       <c r="F10" s="5" t="n">
         <v>10105</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I10" s="40" t="inlineStr">
         <is>
           <t>Messagerie interne : boîtes Dovecot (IMAP/LMTP/Sieve) + webmail (SOGo/Roundcube)</t>
         </is>
@@ -6937,7 +9726,15 @@
       <c r="F11" s="5" t="n">
         <v>10106</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I11" s="40" t="inlineStr">
         <is>
           <t>Backend ToIP (Asterisk, FreePBX, SIP proxy)</t>
         </is>
@@ -6970,7 +9767,15 @@
       <c r="F12" s="5" t="n">
         <v>10107</v>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="n">
+        <v>50001</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>65000:100</t>
+        </is>
+      </c>
+      <c r="I12" s="40" t="inlineStr">
         <is>
           <t>Middlewares, brokers (Kafka, RabbitMQ, bus d'intégration)</t>
         </is>
@@ -6994,265 +9799,7 @@
     <row r="18"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A16:G18"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VRF-DMZ — services exposés (5 VLAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Services accessibles depuis Internet via les VIP publiques CARP portées par le FW. Segmentation par fonction : un compromis sur une fonction n'impacte pas les autres. Tous les flux DMZ → PROD passent obligatoirement par le FW (U-turn).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>VLAN</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Nom</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Préfixe</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>IP début</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>IP fin</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>VNI L2</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Usage</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="27" t="n">
-        <v>200</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>DMZ-FRONT</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>10.3.200.0/24</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>10.3.200.0</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>10.3.200.255</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>10200</v>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Reverse proxy (HAProxy), WAF (BunkerWeb, ModSecurity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="n">
-        <v>201</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>DMZ-WEB</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>10.3.201.0/24</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>10.3.201.0</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>10.3.201.255</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>10201</v>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Serveurs web exposés (vitrine institutionnelle, apps publiques)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
-        <v>202</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>DMZ-MAIL</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>10.3.202.0/24</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>10.3.202.0</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>10.3.202.255</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>10202</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Postfix MX inbound/outbound + Rspamd + ClamAV (anti-spam / anti-virus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="27" t="n">
-        <v>203</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>DMZ-DNS</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>10.3.203.0/24</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>10.3.203.0</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>10.3.203.255</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>10203</v>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>DNS autoritaire public (BIND9 ou NSD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
-        <v>204</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>DMZ-API</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>10.3.204.0/24</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>10.3.204.0</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>10.3.204.255</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>10204</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>API Gateway (exposition d'API publiques, rate limiting)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Scalabilité VRF-DMZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>Bloc 10.3.0.0/16 = 256 /24. 5 /24 utilisés (VLAN 200-204). 251 /24 libres. Extensions possibles : VLAN 210-219 pour une zone DMZ-TRANSIT (relais sécurisés entre DMZ et PROD), VLAN 220-229 pour publication supplémentaire (APIs partenaires, webhooks), VLAN 230+ pour environnements hébergés (ex. filiales).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A13:G15"/>
+    <mergeCell ref="A16:I18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7264,29 +9811,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="54" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VRF-ADMIN — outillage d'administration (7 VLAN)</t>
+          <t>VRF-DMZ — services exposés (5 VLAN)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Outils de gestion et d'exploitation du SI, segmentés par sensibilité. La cellule SOC (VLAN 306) fait partie de cette VRF : elle est opérée par la même population et relève du même régime de privilèges — c'est la même zone de confiance. Son isolement vis-à-vis du reste de l'outillage est assuré par une ACL sur le SVI Vlan306 des Leaf. VLAN Vault isolé pour les secrets et la PKI interne (step-ca).</t>
+          <t>Services accessibles depuis Internet via les VIP publiques CARP portées par le FW. Segmentation par fonction : un compromis sur une fonction n'impacte pas les autres. Tous les flux DMZ → PROD passent obligatoirement par le FW (U-turn).</t>
         </is>
       </c>
     </row>
@@ -7323,281 +9872,244 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>VNI L3</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RD / RT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>Usage</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
-        <v>300</v>
+      <c r="A5" s="27" t="n">
+        <v>200</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ADMIN-CORE</t>
+          <t>DMZ-FRONT</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>10.4.30.0/24</t>
+          <t>10.3.200.0/24</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>10.4.30.0</t>
+          <t>10.3.200.0</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>10.4.30.255</t>
+          <t>10.3.200.255</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>10300</v>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Bastion (Guacamole), PBS, Proxmox Datacenter Manager, ITSM (GLPI)</t>
+        <v>10200</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>50002</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="I5" s="40" t="inlineStr">
+        <is>
+          <t>Reverse proxy (HAProxy), WAF (BunkerWeb, ModSecurity)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
-        <v>301</v>
+      <c r="A6" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ADMIN-CICD</t>
+          <t>DMZ-WEB</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>10.4.31.0/24</t>
+          <t>10.3.201.0/24</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>10.4.31.0</t>
+          <t>10.3.201.0</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>10.4.31.255</t>
+          <t>10.3.201.255</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
-        <v>10301</v>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>GitLab, Jenkins, runners CI/CD, artefacts (Nexus, Harbor)</t>
+        <v>10201</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>50002</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="I6" s="40" t="inlineStr">
+        <is>
+          <t>Serveurs web exposés (vitrine institutionnelle, apps publiques)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
-        <v>302</v>
+      <c r="A7" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ADMIN-OBSERV</t>
+          <t>DMZ-MAIL</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>10.4.32.0/24</t>
+          <t>10.3.202.0/24</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>10.4.32.0</t>
+          <t>10.3.202.0</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>10.4.32.255</t>
+          <t>10.3.202.255</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>10302</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Observabilité (plan NOC) : Grafana Alloy (agents + gateway), Prometheus, Loki, Tempo, Grafana</t>
+        <v>10202</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>50002</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="I7" s="40" t="inlineStr">
+        <is>
+          <t>Postfix MX inbound/outbound + Rspamd + ClamAV (anti-spam / anti-virus)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n">
-        <v>303</v>
+      <c r="A8" s="27" t="n">
+        <v>203</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ADMIN-AAA</t>
+          <t>DMZ-DNS</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>10.4.33.0/24</t>
+          <t>10.3.203.0/24</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>10.4.33.0</t>
+          <t>10.3.203.0</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>10.4.33.255</t>
+          <t>10.3.203.255</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
-        <v>10303</v>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>FreeRADIUS, Keycloak, SSO (identité et authentification centralisées)</t>
+        <v>10203</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>50002</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="I8" s="40" t="inlineStr">
+        <is>
+          <t>DNS autoritaire public (BIND9 ou NSD)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="n">
-        <v>304</v>
+      <c r="A9" s="27" t="n">
+        <v>204</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>ADMIN-AUTOMATE</t>
+          <t>DMZ-API</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>10.4.34.0/24</t>
+          <t>10.3.204.0/24</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>10.4.34.0</t>
+          <t>10.3.204.0</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>10.4.34.255</t>
+          <t>10.3.204.255</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
-        <v>10304</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Ansible, AWX, contrôleurs d'orchestration</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28" t="n">
-        <v>305</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>ADMIN-VAULT</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>10.4.35.0/24</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>10.4.35.0</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>10.4.35.255</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>10305</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>HashiCorp Vault (secrets) + step-ca (PKI interne : émission + provisioning ACME)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>ADMIN-SOC</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>10.4.36.0/24</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>10.4.36.0</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>10.4.36.255</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>10306</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Wazuh (SIEM/EDR), MISP (TI), DFIR-IRIS (SIRP), Shuffle (SOAR), Malcolm (NSM) + sondes Hedgehog</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Note sur le VLAN SOC et l'arbitrage VRF-SOC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>La promotion du SOC en VRF dédiée a été étudiée puis écartée. Deux arguments plaidaient pour : la polarité des flux y est inversée ('tout le SI vers le SOC' pour la collecte) et le SOC héberge les preuves d'une compromission. Trois arguments ont tranché contre : SOC et outillage d'administration relèvent de la même zone de confiance ; le coût d'une VRF pour un unique VLAN est disproportionné (L3VNI, RD/RT, 4 sous-interfaces de handoff par FW et par Spine, jeu de règles) et transforme en flux firewall tous les échanges légitimes du SOC avec Vault, l'AAA et Ansible ; enfin la promotion reste réversible à faible coût. CONTREPARTIE ASSUMÉE : les flux ADMIN vers SOC sont routés par la fabric, sans inspection firewall. COMPENSATION : ACL sur le SVI Vlan306 des Leaf n'autorisant que les ports de collecte depuis VRF-ADMIN, accès analyste réservé au bastion. Identifiants réservés pour une promotion ultérieure : 10.5.0.0/16, RD/RT 65000:400, VNI L3 50005, plage 4xx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Scalabilité VRF-ADMIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>Bloc 10.4.0.0/16 = 256 /24. 7 /24 utilisés (VLAN 300-306). 249 /24 libres. CONVENTION DU 3e OCTET POUR CETTE PLAGE : 3e octet = 30 + (VLAN - 300), soit 10.4.30 pour le VLAN 300 jusqu'à 10.4.36 pour le VLAN 306, un octet ne pouvant excéder 255. Méconnaître cette exception produit des adresses invalides du type 10.4.302.10. Extensions : VLAN 307-310 pour outillage spécifique (DFIR, forensics, pentest interne). Granularité SOC niveau ++ en cas de promotion : 401 SIEM, 402 NSM, 403 TI, 404 SIRP, 405 SOAR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+        <v>10204</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>50002</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>65000:200</t>
+        </is>
+      </c>
+      <c r="I9" s="40" t="inlineStr">
+        <is>
+          <t>API Gateway (exposition d'API publiques, rate limiting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Scalabilité VRF-DMZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Bloc 10.3.0.0/16 = 256 /24. 5 /24 utilisés (VLAN 200-204). 251 /24 libres. Extensions possibles : VLAN 210-219 pour une zone DMZ-TRANSIT (relais sécurisés entre DMZ et PROD), VLAN 220-229 pour publication supplémentaire (APIs partenaires, webhooks), VLAN 230+ pour environnements hébergés (ex. filiales).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A15:G17"/>
-    <mergeCell ref="A20:G22"/>
+  <mergeCells count="1">
+    <mergeCell ref="A13:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7609,661 +10121,408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Management des équipements — VRF-MGMT, segments MGMT-LAN et loopbacks</t>
+          <t>VRF-ADMIN — outillage d'administration (7 VLAN)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Le management obéit à deux méthodes selon la nature de l'équipement. Les équipements capables de router (Spine, Leaf, Core, Distribution, FW) s'administrent via leur Loopback0, joignable par le routage et insensible à la perte d'un lien. Les switches Access, purement L2, utilisent une SVI dans le VLAN 999 local à leur bloc. La VRF-MGMT ne dessert donc plus que les interfaces d'administration des hyperviseurs. L'identifiant 999 est réutilisé dans trois domaines de diffusion distincts (fabric DC, bloc LAN 1, bloc LAN 2) : un numéro de VLAN n'a de portée que locale au domaine qui le porte.</t>
+          <t>Outils de gestion et d'exploitation du SI, segmentés par sensibilité. La cellule SOC (VLAN 306) fait partie de cette VRF : elle est opérée par la même population et relève du même régime de privilèges — c'est la même zone de confiance. Son isolement vis-à-vis du reste de l'outillage est assuré par une ACL sur le SVI Vlan306 des Leaf. VLAN Vault isolé pour les secrets et la PKI interne (step-ca).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Segments de management</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>VLAN</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Préfixe</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>IP début</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>IP fin</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>VNI L2</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>VNI L3</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RD / RT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Usage</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Préfixe</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>VLAN</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Passerelle</t>
+      <c r="A5" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ADMIN-CORE</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>10.4.30.0/24</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>10.4.30.0</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>10.4.30.255</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="I5" s="40" t="inlineStr">
+        <is>
+          <t>Bastion (Guacamole), PBS, Proxmox Datacenter Manager, ITSM (GLPI)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>MGMT-DC (fabric, VNI 10999)</t>
-        </is>
+      <c r="A6" s="28" t="n">
+        <v>301</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>10.254.0.0/24</t>
+          <t>ADMIN-CICD</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>10.254.0.1 — anycast sur les Leaf</t>
+          <t>10.4.31.0/24</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>10.4.31.0</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>10.4.31.255</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10301</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="I6" s="40" t="inlineStr">
+        <is>
+          <t>GitLab, Jenkins, runners CI/CD, artefacts (Nexus, Harbor)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>MGMT-LAN bloc 1 (local)</t>
-        </is>
+      <c r="A7" s="28" t="n">
+        <v>302</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>10.254.1.0/24</t>
+          <t>ADMIN-OBSERV</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>10.254.1.1 — VIP VRRP sur DIST-1/DIST-2</t>
+          <t>10.4.32.0/24</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>10.4.32.0</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>10.4.32.255</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>10302</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="I7" s="40" t="inlineStr">
+        <is>
+          <t>Observabilité (plan NOC) : Grafana Alloy (agents + gateway), Prometheus, Loki, Tempo, Grafana</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>MGMT-LAN bloc 2 (local)</t>
-        </is>
+      <c r="A8" s="28" t="n">
+        <v>303</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>10.254.2.0/24</t>
+          <t>ADMIN-AAA</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>10.254.2.1 — VIP VRRP sur DIST-3/DIST-4</t>
+          <t>10.4.33.0/24</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>10.4.33.0</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>10.4.33.255</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>10303</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="I8" s="40" t="inlineStr">
+        <is>
+          <t>FreeRADIUS, Keycloak, SSO (identité et authentification centralisées)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Loopbacks d'administration L3</t>
-        </is>
+      <c r="A9" s="28" t="n">
+        <v>304</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>10.0.0.0/24</t>
+          <t>ADMIN-AUTOMATE</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Routé via OSPF (cf. onglet Loopbacks)</t>
+          <t>10.4.34.0/24</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>10.4.34.0</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>10.4.34.255</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10304</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="I9" s="40" t="inlineStr">
+        <is>
+          <t>Ansible, AWX, contrôleurs d'orchestration</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
+        <v>305</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ADMIN-VAULT</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>10.4.35.0/24</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>10.4.35.0</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>10.4.35.255</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10305</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="I10" s="40" t="inlineStr">
+        <is>
+          <t>HashiCorp Vault (secrets) + step-ca (PKI interne : émission + provisioning ACME)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Plan IP management</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Équipement</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Interface</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Commentaire</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>SPINE-1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.1/32</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; Management1 non câblé (pas d'OOB)</t>
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ADMIN-SOC</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>10.4.36.0/24</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>10.4.36.0</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>10.4.36.255</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>50003</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>65000:300</t>
+        </is>
+      </c>
+      <c r="I11" s="40" t="inlineStr">
+        <is>
+          <t>Wazuh (SIEM/EDR), MISP (TI), DFIR-IRIS (SIRP), Shuffle (SOAR), Malcolm (NSM) + sondes Hedgehog</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>SPINE-2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.2/32</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; Management1 non câblé (pas d'OOB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.11/32</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-2</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.12/32</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>LEAF-3</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.13/32</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; porte aussi le SVI anycast Vlan999 (10.254.0.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>CORE-1</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.21/32</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; aucun SVI de management</t>
-        </is>
-      </c>
-    </row>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Note sur le VLAN SOC et l'arbitrage VRF-SOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>La promotion du SOC en VRF dédiée a été étudiée puis écartée. Deux arguments plaidaient pour : la polarité des flux y est inversée ('tout le SI vers le SOC' pour la collecte) et le SOC héberge les preuves d'une compromission. Trois arguments ont tranché contre : SOC et outillage d'administration relèvent de la même zone de confiance ; le coût d'une VRF pour un unique VLAN est disproportionné (L3VNI, RD/RT, 4 sous-interfaces de handoff par FW et par Spine, jeu de règles) et transforme en flux firewall tous les échanges légitimes du SOC avec Vault, l'AAA et Ansible ; enfin la promotion reste réversible à faible coût. CONTREPARTIE ASSUMÉE : les flux ADMIN vers SOC sont routés par la fabric, sans inspection firewall. COMPENSATION : ACL sur le SVI Vlan306 des Leaf n'autorisant que les ports de collecte depuis VRF-ADMIN, accès analyste réservé au bastion. Identifiants réservés pour une promotion ultérieure : 10.5.0.0/16, RD/RT 65000:400, VNI L3 50005, plage 4xx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>CORE-2</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.22/32</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; aucun SVI de management</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>DIST-1</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.31/32</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; SVI Vlan999 10.254.1.2 (VRRP master bloc 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>DIST-2</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.32/32</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; SVI Vlan999 10.254.1.3 (VRRP backup bloc 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>DIST-3</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.33/32</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; SVI Vlan999 10.254.2.2 (VRRP master bloc 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>DIST-4</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.34/32</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Admin in-band ; SVI Vlan999 10.254.2.3 (VRRP backup bloc 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>FW-1</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.41/32</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI ; aucune interface physique libre pour un port dédié</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>FW-2</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Loopback0</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>10.0.0.42/32</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI ; aucune interface physique libre pour un port dédié</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>ACC-1</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan999</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>10.254.1.41/24</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>L2 pur ; ip default-gateway 10.254.1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>ACC-2</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan999</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>10.254.1.42/24</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>L2 pur ; ip default-gateway 10.254.1.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>ACC-3</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan999</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>10.254.2.43/24</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>L2 pur ; ip default-gateway 10.254.2.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>ACC-4</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>SVI Vlan999</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>10.254.2.44/24</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>L2 pur ; ip default-gateway 10.254.2.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-1</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0 (VLAN 999)</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.61/24</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-2</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0 (VLAN 999)</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.62/24</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>ProxmoxVE-3</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>vmbr0 (VLAN 999)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>10.254.0.63/24</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>SSH + webGUI 8006 ; GW anycast 10.254.0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Plan interne d'un /24 de management</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>.1 passerelle (anycast Leaf ou VIP VRRP)  •  .2/.3 SVI Distribution A/B  •  .41-.49 switches Access  •  .61-.69 hyperviseurs  •  .100-.254 réserve</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr"/>
-      <c r="C35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="21" t="n"/>
-      <c r="C36" s="7" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="n"/>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Scalabilité et absence de réseau hors-bande</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>Bloc 10.254.0.0/16 = 256 /24, dont 3 utilisés (10.254.0 fabric DC, 10.254.1 bloc LAN 1, 10.254.2 bloc LAN 2) et 253 libres. Un /24 supplémentaire par nouveau bloc de Distribution. ABSENCE D'OOB : la maquette ne comporte aucun réseau d'administration hors-bande. Les interfaces Management1 des Arista existent mais ne sont raccordées à aucun lien, et les FW n'ont plus d'interface physique disponible (em0 pfsync, em1 WAN, em2/em3 Spine, em4/em5 Core). L'administration est donc entièrement in-band. En production, on disposerait d'un réseau OOB physiquement distinct (switch dédié, IPMI/BMC, console série) pour conserver la main lorsque le plan de données est en panne. Simplification acceptable ici car l'accès console reste disponible depuis GNS3, mais limite à connaître.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>Scalabilité VRF-ADMIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>Bloc 10.4.0.0/16 = 256 /24. 7 /24 utilisés (VLAN 300-306). 249 /24 libres. CONVENTION DU 3e OCTET POUR CETTE PLAGE : 3e octet = 30 + (VLAN - 300), soit 10.4.30 pour le VLAN 300 jusqu'à 10.4.36 pour le VLAN 306, un octet ne pouvant excéder 255. Méconnaître cette exception produit des adresses invalides du type 10.4.302.10. Extensions : VLAN 307-310 pour outillage spécifique (DFIR, forensics, pentest interne). Granularité SOC niveau ++ en cas de promotion : 401 SIEM, 402 NSM, 403 TI, 404 SIRP, 405 SOAR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A40:D43"/>
+  <mergeCells count="2">
+    <mergeCell ref="A20:I22"/>
+    <mergeCell ref="A15:I17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
